--- a/SNTL_FeatureList.xlsx
+++ b/SNTL_FeatureList.xlsx
@@ -42,13 +42,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="001F3864"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
+      <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -144,26 +144,23 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -172,7 +169,10 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -184,43 +184,49 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -592,12 +598,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
@@ -637,7 +643,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>설명</t>
+          <t>기능 설명</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -656,72 +662,84 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>로그인/인증</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>시스템 접속을 위한 인증 처리. JWT 기반 Stateless 인증 방식 사용.</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5" ht="19" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr"/>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>로그인</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>사용자가 시스템에 접속하기 위해 자격증명을 검증하는 기능.</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr"/>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6" ht="29" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>1.1.1</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr"/>
+      <c r="B6" s="10" t="inlineStr"/>
       <c r="C6" s="11" t="inlineStr"/>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>ID/PW 로그인</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr"/>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>아이디와 비밀번호로 로그인</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>아이디와 비밀번호를 입력하여 로그인. 성공 시 Access Token(30분)과 Refresh Token(7일)을 발급함. 비밀번호는 BCrypt로 해싱하여 검증.</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>회원/운영자/관리자</t>
         </is>
@@ -731,28 +749,28 @@
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr"/>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr"/>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>1.1.2</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr"/>
+      <c r="B7" s="10" t="inlineStr"/>
       <c r="C7" s="11" t="inlineStr"/>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>소셜 로그인</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr"/>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>OAuth2 소셜 계정으로 로그인 (개인회원)</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Google·Kakao 등 OAuth2 소셜 계정으로 인증. 최초 로그인 시 회원가입 연동 처리. 개인회원 전용 기능.</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>개인회원</t>
         </is>
@@ -762,51 +780,59 @@
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>소셜 플랫폼 추후 확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr"/>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr"/>
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>ID/PW 찾기</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="8" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>로그인 정보를 분실했을 때 본인 인증을 통해 ID 확인 및 PW 재설정을 지원하는 기능.</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>1.2.1</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr"/>
+      <c r="B9" s="10" t="inlineStr"/>
       <c r="C9" s="11" t="inlineStr"/>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>ID 찾기</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr"/>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>이름+휴대폰 인증으로 로그인ID 확인</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>이름과 휴대폰번호를 입력하고 SMS 인증번호를 통해 본인 확인 후 로그인 ID를 화면에 표시. 법인회원은 법인명 + 사업자번호로 확인.</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>회원</t>
         </is>
@@ -816,28 +842,28 @@
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>1.2.2</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr"/>
+      <c r="B10" s="10" t="inlineStr"/>
       <c r="C10" s="11" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>PW 재설정</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr"/>
-      <c r="F10" s="11" t="inlineStr">
-        <is>
-          <t>본인인증 후 비밀번호 재설정</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>이메일 또는 SMS 인증을 통해 본인 확인 후 새 비밀번호를 설정. 새 비밀번호는 영문+숫자+특수문자 8자 이상 조건 적용.</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>회원</t>
         </is>
@@ -847,125 +873,137 @@
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr"/>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr"/>
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>로그아웃</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr"/>
-      <c r="E11" s="8" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr"/>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>JWT 토큰 무효화 (Refresh Token 삭제)</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
+          <t>로그아웃 요청 시 Redis에 저장된 Refresh Token을 삭제하고 Access Token을 블랙리스트에 등록하여 재사용을 차단.</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>회원관리</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>개인회원·법인회원·관리자 계정의 등록, 수정, 조회, 탈퇴 등 회원 전반을 관리하는 기능.</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr"/>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr"/>
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>개인회원</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr"/>
-      <c r="G13" s="8" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>B2C 개인 사용자의 회원가입부터 정보관리·탈퇴까지 전 생애주기를 관리.</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr"/>
+      <c r="I13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>2.1.1</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr"/>
+      <c r="B14" s="10" t="inlineStr"/>
       <c r="C14" s="11" t="inlineStr"/>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>회원가입</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr"/>
-      <c r="F14" s="11" t="inlineStr"/>
-      <c r="G14" s="11" t="inlineStr"/>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>개인회원이 서비스 이용을 위해 계정을 생성하는 절차.</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr"/>
       <c r="H14" s="13" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr"/>
-    </row>
-    <row r="15" ht="18" customHeight="1">
+      <c r="I14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15" ht="26" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
         <is>
           <t>2.1.1.1</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr"/>
-      <c r="C15" s="15" t="inlineStr"/>
-      <c r="D15" s="15" t="inlineStr"/>
+      <c r="C15" s="16" t="inlineStr"/>
+      <c r="D15" s="16" t="inlineStr"/>
       <c r="E15" s="16" t="inlineStr">
         <is>
           <t>본인확인</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
-        <is>
-          <t>이름·생년월일·휴대폰 인증</t>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>이름·생년월일·휴대폰번호를 입력하고 SMS 인증번호로 본인 확인. 중복 가입 방지를 위해 동일 휴대폰번호로 기존 계정 존재 여부 체크.</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
@@ -980,23 +1018,23 @@
       </c>
       <c r="I15" s="15" t="inlineStr"/>
     </row>
-    <row r="16" ht="18" customHeight="1">
+    <row r="16" ht="28" customHeight="1">
       <c r="A16" s="14" t="inlineStr">
         <is>
           <t>2.1.1.2</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr"/>
-      <c r="C16" s="15" t="inlineStr"/>
-      <c r="D16" s="15" t="inlineStr"/>
+      <c r="C16" s="16" t="inlineStr"/>
+      <c r="D16" s="16" t="inlineStr"/>
       <c r="E16" s="16" t="inlineStr">
         <is>
           <t>개인정보 입력</t>
         </is>
       </c>
-      <c r="F16" s="15" t="inlineStr">
-        <is>
-          <t>이름/생년월일/연락처/주소/이메일 입력</t>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>본인확인 완료 후 로그인ID·비밀번호·이메일·주소를 입력하여 계정 생성. 로그인ID와 이메일은 중복 불가. 주소는 국가코드+우편번호+주소+상세주소로 구성.</t>
         </is>
       </c>
       <c r="G16" s="15" t="inlineStr">
@@ -1011,23 +1049,23 @@
       </c>
       <c r="I16" s="15" t="inlineStr"/>
     </row>
-    <row r="17" ht="18" customHeight="1">
+    <row r="17" ht="27" customHeight="1">
       <c r="A17" s="14" t="inlineStr">
         <is>
           <t>2.1.1.3</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr"/>
-      <c r="C17" s="15" t="inlineStr"/>
-      <c r="D17" s="15" t="inlineStr"/>
+      <c r="C17" s="16" t="inlineStr"/>
+      <c r="D17" s="16" t="inlineStr"/>
       <c r="E17" s="16" t="inlineStr">
         <is>
           <t>소셜 로그인 연동 가입</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>소셜 계정으로 회원가입 본인확인</t>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>소셜 계정(Google 등)으로 최초 접근 시 소셜 인증 후 추가 정보(이름·주소·이메일)를 입력하여 계정 생성. 이후 소셜 로그인으로 자동 인증.</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
@@ -1042,26 +1080,26 @@
       </c>
       <c r="I17" s="15" t="inlineStr"/>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>2.1.2</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr"/>
+      <c r="B18" s="10" t="inlineStr"/>
       <c r="C18" s="11" t="inlineStr"/>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>회원정보 수정</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr"/>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>이름/생년월일/휴대폰/주소/이메일 수정</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>이름·생년월일·휴대폰번호·주소·이메일 주소 수정 가능. 로그인ID는 변경 불가. 수정 완료 후 최종수정일시 갱신.</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>개인회원</t>
         </is>
@@ -1071,28 +1109,28 @@
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr"/>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>2.1.3</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr"/>
+      <c r="B19" s="10" t="inlineStr"/>
       <c r="C19" s="11" t="inlineStr"/>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>회원 등급 조회</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr"/>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>발송횟수 기반 등급 및 할인율 확인</t>
-        </is>
-      </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>발송횟수 등 이용 실적에 따라 자동 부여된 등급(BASIC/SILVER/GOLD/VIP) 확인. 등급별 운송비 할인율 정보를 함께 표시.</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>개인회원</t>
         </is>
@@ -1102,28 +1140,32 @@
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr"/>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>등급기준 추후 확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="25" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>2.1.4</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr"/>
+      <c r="B20" s="10" t="inlineStr"/>
       <c r="C20" s="11" t="inlineStr"/>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>잔액 충전</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr"/>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>선불 잔액 충전</t>
-        </is>
-      </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>선불 방식으로 서비스 이용 잔액을 충전. 충전 금액은 청구서 결제에 사용 가능. 충전 후 잔액 및 충전 이력을 확인할 수 있음.</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>개인회원</t>
         </is>
@@ -1133,28 +1175,28 @@
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr"/>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21" ht="23" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>2.1.5</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr"/>
+      <c r="B21" s="10" t="inlineStr"/>
       <c r="C21" s="11" t="inlineStr"/>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>잔액 환불</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr"/>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>충전 잔액 환불 요청</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>충전 잔액 중 미사용 금액에 대해 환불 요청. 환불 처리는 관리자 검토 후 진행되며 청구서에 반영.</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>개인회원</t>
         </is>
@@ -1164,28 +1206,28 @@
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>2.1.6</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr"/>
+      <c r="B22" s="10" t="inlineStr"/>
       <c r="C22" s="11" t="inlineStr"/>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>청구내역 조회</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr"/>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>청구 이력 목록 조회</t>
-        </is>
-      </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>내 계정에 발행된 청구서 목록과 항목별 청구 이력 조회. 기간·운송수단별 필터링 가능하며 청구서 PDF 출력 지원.</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>개인회원</t>
         </is>
@@ -1195,28 +1237,28 @@
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr"/>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23" ht="29" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>2.1.7</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr"/>
+      <c r="B23" s="10" t="inlineStr"/>
       <c r="C23" s="11" t="inlineStr"/>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>회원탈퇴</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr"/>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>개인정보 Null 처리, 로그인ID만 보존</t>
-        </is>
-      </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>본인이 직접 탈퇴 신청. 개인정보(이름·생년월일·연락처·주소·이메일)는 Null 처리하고 로그인ID만 보존(Soft Delete). 탈퇴 후 동일 ID로 재가입 불가.</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>개인회원</t>
         </is>
@@ -1226,32 +1268,32 @@
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>Soft Delete</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+    <row r="24" ht="23" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>2.1.8</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr"/>
+      <c r="B24" s="10" t="inlineStr"/>
       <c r="C24" s="11" t="inlineStr"/>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>개인정보 활용동의</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr"/>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>서비스 이용 약관 및 개인정보 동의 관리</t>
-        </is>
-      </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>서비스 이용 약관 및 개인정보 처리방침 동의 여부 관리. 필수 동의 항목 미동의 시 서비스 이용 제한.</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>개인회원</t>
         </is>
@@ -1261,71 +1303,79 @@
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr"/>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr"/>
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>법인회원</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr"/>
-      <c r="E25" s="8" t="inlineStr"/>
-      <c r="F25" s="8" t="inlineStr"/>
-      <c r="G25" s="8" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr"/>
+      <c r="E25" s="7" t="inlineStr"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>B2B 법인 고객의 가입부터 조직(부서)·관리자 관리, 탈퇴까지 처리.</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr"/>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>2.2.1</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr"/>
+      <c r="B26" s="10" t="inlineStr"/>
       <c r="C26" s="11" t="inlineStr"/>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>법인 회원가입</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr"/>
-      <c r="F26" s="11" t="inlineStr"/>
-      <c r="G26" s="11" t="inlineStr"/>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>법인 계정 생성 절차. 가입 후 관리자 심사 승인 시 계정 활성화.</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr"/>
       <c r="H26" s="13" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
+      <c r="I26" s="10" t="inlineStr"/>
+    </row>
+    <row r="27" ht="21" customHeight="1">
       <c r="A27" s="14" t="inlineStr">
         <is>
           <t>2.2.1.1</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr"/>
-      <c r="C27" s="15" t="inlineStr"/>
-      <c r="D27" s="15" t="inlineStr"/>
+      <c r="C27" s="16" t="inlineStr"/>
+      <c r="D27" s="16" t="inlineStr"/>
       <c r="E27" s="16" t="inlineStr">
         <is>
           <t>법인관리자 본인확인</t>
         </is>
       </c>
-      <c r="F27" s="15" t="inlineStr">
-        <is>
-          <t>법인관리자 이름·생년월일·휴대폰 인증</t>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>법인관리자의 이름·생년월일·휴대폰번호를 입력하고 SMS 인증번호로 본인 확인.</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
@@ -1340,23 +1390,23 @@
       </c>
       <c r="I27" s="15" t="inlineStr"/>
     </row>
-    <row r="28" ht="18" customHeight="1">
+    <row r="28" ht="21" customHeight="1">
       <c r="A28" s="14" t="inlineStr">
         <is>
           <t>2.2.1.2</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr"/>
-      <c r="C28" s="15" t="inlineStr"/>
-      <c r="D28" s="15" t="inlineStr"/>
+      <c r="C28" s="16" t="inlineStr"/>
+      <c r="D28" s="16" t="inlineStr"/>
       <c r="E28" s="16" t="inlineStr">
         <is>
           <t>법인정보 입력</t>
         </is>
       </c>
-      <c r="F28" s="15" t="inlineStr">
-        <is>
-          <t>법인명/대표자명/사업자번호/주소 입력</t>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>법인명·대표자명·사업자등록번호·대표전화·이메일·주소 입력. 사업자등록번호 중복 체크.</t>
         </is>
       </c>
       <c r="G28" s="15" t="inlineStr">
@@ -1371,23 +1421,23 @@
       </c>
       <c r="I28" s="15" t="inlineStr"/>
     </row>
-    <row r="29" ht="18" customHeight="1">
+    <row r="29" ht="25" customHeight="1">
       <c r="A29" s="14" t="inlineStr">
         <is>
           <t>2.2.1.3</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr"/>
-      <c r="C29" s="15" t="inlineStr"/>
-      <c r="D29" s="15" t="inlineStr"/>
+      <c r="C29" s="16" t="inlineStr"/>
+      <c r="D29" s="16" t="inlineStr"/>
       <c r="E29" s="16" t="inlineStr">
         <is>
           <t>첨부파일 업로드</t>
         </is>
       </c>
-      <c r="F29" s="15" t="inlineStr">
-        <is>
-          <t>사업자등록증 등 심사 파일 업로드</t>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>사업자등록증 등 심사에 필요한 증빙 서류 파일 업로드. 파일은 MinIO에 저장되며 관리자가 열람하여 승인·거부 결정.</t>
         </is>
       </c>
       <c r="G29" s="15" t="inlineStr">
@@ -1400,25 +1450,29 @@
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I29" s="15" t="inlineStr"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>허용 파일: PDF·JPG·PNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="23" customHeight="1">
       <c r="A30" s="14" t="inlineStr">
         <is>
           <t>2.2.1.4</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr"/>
-      <c r="C30" s="15" t="inlineStr"/>
-      <c r="D30" s="15" t="inlineStr"/>
+      <c r="C30" s="16" t="inlineStr"/>
+      <c r="D30" s="16" t="inlineStr"/>
       <c r="E30" s="16" t="inlineStr">
         <is>
           <t>부서정보 입력</t>
         </is>
       </c>
-      <c r="F30" s="15" t="inlineStr">
-        <is>
-          <t>소속 부서명 입력</t>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>가입과 함께 최초 부서명 및 부서관리자 정보를 입력. 부서 추가는 가입 승인 후 별도 관리 메뉴에서 처리.</t>
         </is>
       </c>
       <c r="G30" s="15" t="inlineStr">
@@ -1433,26 +1487,26 @@
       </c>
       <c r="I30" s="15" t="inlineStr"/>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>2.2.2</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr"/>
+      <c r="B31" s="10" t="inlineStr"/>
       <c r="C31" s="11" t="inlineStr"/>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>법인정보 수정</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr"/>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>법인 대표명/주소/전화/이메일 수정</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>법인 대표자명·법인주소·대표전화·이메일 수정 가능. 법인명·사업자번호는 변경 불가(변경 필요 시 관리자 문의).</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>법인관리자</t>
         </is>
@@ -1462,28 +1516,28 @@
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>2.2.3</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr"/>
+      <c r="B32" s="10" t="inlineStr"/>
       <c r="C32" s="11" t="inlineStr"/>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>법인관리자 정보수정</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr"/>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>법인관리자 이름/연락처/주소 수정</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>법인관리자 본인의 이름·생년월일·휴대폰번호·주소·이메일 수정.</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>법인관리자</t>
         </is>
@@ -1493,28 +1547,28 @@
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I32" s="11" t="inlineStr"/>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33" ht="25" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>2.2.4</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr"/>
+      <c r="B33" s="10" t="inlineStr"/>
       <c r="C33" s="11" t="inlineStr"/>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>부서 관리</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr"/>
-      <c r="F33" s="11" t="inlineStr">
-        <is>
-          <t>부서명 추가/수정/삭제</t>
-        </is>
-      </c>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>법인 소속 부서를 추가·수정·삭제. 삭제 시 부서ID만 보존하고 부서명 등 정보는 Null 처리(Soft Delete).</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>법인관리자</t>
         </is>
@@ -1524,28 +1578,28 @@
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I33" s="11" t="inlineStr"/>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr"/>
+    </row>
+    <row r="34" ht="19" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>2.2.5</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr"/>
+      <c r="B34" s="10" t="inlineStr"/>
       <c r="C34" s="11" t="inlineStr"/>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>부서관리자 정보수정</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr"/>
-      <c r="F34" s="11" t="inlineStr">
-        <is>
-          <t>부서관리자 이름/연락처/주소 수정</t>
-        </is>
-      </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>부서관리자 본인의 이름·생년월일·휴대폰번호·주소·이메일 수정.</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>부서관리자</t>
         </is>
@@ -1555,28 +1609,28 @@
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I34" s="11" t="inlineStr"/>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr"/>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>2.2.6</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr"/>
+      <c r="B35" s="10" t="inlineStr"/>
       <c r="C35" s="11" t="inlineStr"/>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>법인 회원탈퇴</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr"/>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t>법인·관리자·부서 Soft Delete 처리</t>
-        </is>
-      </c>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>법인관리자가 탈퇴 시 법인·법인관리자·부서·부서관리자 전체 Soft Delete 처리. 법인ID·법인관리자ID·부서ID·부서관리자ID만 보존하고 개인정보는 전부 Null 처리. 법인증빙파일은 완전 삭제.</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
         <is>
           <t>법인관리자</t>
         </is>
@@ -1586,51 +1640,55 @@
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I35" s="11" t="inlineStr"/>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr"/>
+    </row>
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr"/>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr"/>
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr"/>
-      <c r="E36" s="8" t="inlineStr"/>
-      <c r="F36" s="8" t="inlineStr"/>
-      <c r="G36" s="8" t="inlineStr"/>
-      <c r="H36" s="6" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr"/>
+      <c r="E36" s="7" t="inlineStr"/>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>시스템 관리자가 회원 계정 및 운송비용 정책을 관리하는 기능.</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr"/>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37" ht="25" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>2.3.1</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr"/>
+      <c r="B37" s="10" t="inlineStr"/>
       <c r="C37" s="11" t="inlineStr"/>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>개인회원 관리</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr"/>
-      <c r="F37" s="11" t="inlineStr">
-        <is>
-          <t>회원별 등급·할인율 조회 및 설정</t>
-        </is>
-      </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>전체 개인회원 목록 조회 및 회원별 등급·할인율 조회·설정. 발송횟수 기준 등급을 수동으로 조정하거나 할인율을 직접 설정 가능.</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
@@ -1640,48 +1698,52 @@
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr"/>
+    </row>
+    <row r="38" ht="21" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>2.3.2</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr"/>
+      <c r="B38" s="10" t="inlineStr"/>
       <c r="C38" s="11" t="inlineStr"/>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>법인 심사</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr"/>
-      <c r="F38" s="11" t="inlineStr"/>
-      <c r="G38" s="11" t="inlineStr"/>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>법인 회원가입 신청 건에 대해 증빙서류를 확인하고 승인 또는 거부하는 절차.</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr"/>
       <c r="H38" s="13" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I38" s="11" t="inlineStr"/>
-    </row>
-    <row r="39" ht="18" customHeight="1">
+      <c r="I38" s="10" t="inlineStr"/>
+    </row>
+    <row r="39" ht="21" customHeight="1">
       <c r="A39" s="14" t="inlineStr">
         <is>
           <t>2.3.2.1</t>
         </is>
       </c>
       <c r="B39" s="15" t="inlineStr"/>
-      <c r="C39" s="15" t="inlineStr"/>
-      <c r="D39" s="15" t="inlineStr"/>
+      <c r="C39" s="16" t="inlineStr"/>
+      <c r="D39" s="16" t="inlineStr"/>
       <c r="E39" s="16" t="inlineStr">
         <is>
           <t>첨부파일 확인</t>
         </is>
       </c>
-      <c r="F39" s="15" t="inlineStr">
-        <is>
-          <t>업로드된 사업자등록증 등 열람</t>
+      <c r="F39" s="17" t="inlineStr">
+        <is>
+          <t>가입 시 업로드된 사업자등록증 등 증빙파일을 MinIO에서 불러와 관리자가 열람.</t>
         </is>
       </c>
       <c r="G39" s="15" t="inlineStr">
@@ -1696,23 +1758,23 @@
       </c>
       <c r="I39" s="15" t="inlineStr"/>
     </row>
-    <row r="40" ht="18" customHeight="1">
+    <row r="40" ht="22" customHeight="1">
       <c r="A40" s="14" t="inlineStr">
         <is>
           <t>2.3.2.2</t>
         </is>
       </c>
       <c r="B40" s="15" t="inlineStr"/>
-      <c r="C40" s="15" t="inlineStr"/>
-      <c r="D40" s="15" t="inlineStr"/>
+      <c r="C40" s="16" t="inlineStr"/>
+      <c r="D40" s="16" t="inlineStr"/>
       <c r="E40" s="16" t="inlineStr">
         <is>
           <t>승인 처리</t>
         </is>
       </c>
-      <c r="F40" s="15" t="inlineStr">
-        <is>
-          <t>법인 계정 활성화</t>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>심사 통과 시 법인 계정 상태를 ACTIVE로 변경하고 법인관리자에게 승인 안내 알림 발송.</t>
         </is>
       </c>
       <c r="G40" s="15" t="inlineStr">
@@ -1727,23 +1789,23 @@
       </c>
       <c r="I40" s="15" t="inlineStr"/>
     </row>
-    <row r="41" ht="18" customHeight="1">
+    <row r="41" ht="25" customHeight="1">
       <c r="A41" s="14" t="inlineStr">
         <is>
           <t>2.3.2.3</t>
         </is>
       </c>
       <c r="B41" s="15" t="inlineStr"/>
-      <c r="C41" s="15" t="inlineStr"/>
-      <c r="D41" s="15" t="inlineStr"/>
+      <c r="C41" s="16" t="inlineStr"/>
+      <c r="D41" s="16" t="inlineStr"/>
       <c r="E41" s="16" t="inlineStr">
         <is>
           <t>거부 처리</t>
         </is>
       </c>
-      <c r="F41" s="15" t="inlineStr">
-        <is>
-          <t>심사 거부 및 사유 통보</t>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>심사 거부 시 approval_status를 REJECTED로 변경하고 거부 사유를 법인관리자에게 알림. 거부 후 재신청 가능.</t>
         </is>
       </c>
       <c r="G41" s="15" t="inlineStr">
@@ -1758,46 +1820,50 @@
       </c>
       <c r="I41" s="15" t="inlineStr"/>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>2.3.3</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr"/>
+      <c r="B42" s="10" t="inlineStr"/>
       <c r="C42" s="11" t="inlineStr"/>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="D42" s="11" t="inlineStr">
         <is>
           <t>운송비용 관리</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr"/>
-      <c r="F42" s="11" t="inlineStr"/>
-      <c r="G42" s="11" t="inlineStr"/>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>회원별 서비스 운송비 할인율 및 영업이익율을 등록·수정하는 기능.</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr"/>
       <c r="H42" s="13" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I42" s="11" t="inlineStr"/>
-    </row>
-    <row r="43" ht="18" customHeight="1">
+      <c r="I42" s="10" t="inlineStr"/>
+    </row>
+    <row r="43" ht="27" customHeight="1">
       <c r="A43" s="14" t="inlineStr">
         <is>
           <t>2.3.3.1</t>
         </is>
       </c>
       <c r="B43" s="15" t="inlineStr"/>
-      <c r="C43" s="15" t="inlineStr"/>
-      <c r="D43" s="15" t="inlineStr"/>
+      <c r="C43" s="16" t="inlineStr"/>
+      <c r="D43" s="16" t="inlineStr"/>
       <c r="E43" s="16" t="inlineStr">
         <is>
           <t>개인회원 운송비 등록/수정</t>
         </is>
       </c>
-      <c r="F43" s="15" t="inlineStr">
-        <is>
-          <t>개인회원별 운송비 할인율 설정</t>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t>개인회원별로 AIR·SEA·CIR·CCL 서비스에 대한 할인율(%)과 영업이익율(%) 설정. 적용 시작일과 종료일을 지정하여 기간 관리 가능.</t>
         </is>
       </c>
       <c r="G43" s="15" t="inlineStr">
@@ -1812,23 +1878,23 @@
       </c>
       <c r="I43" s="15" t="inlineStr"/>
     </row>
-    <row r="44" ht="18" customHeight="1">
+    <row r="44" ht="26" customHeight="1">
       <c r="A44" s="14" t="inlineStr">
         <is>
           <t>2.3.3.2</t>
         </is>
       </c>
       <c r="B44" s="15" t="inlineStr"/>
-      <c r="C44" s="15" t="inlineStr"/>
-      <c r="D44" s="15" t="inlineStr"/>
+      <c r="C44" s="16" t="inlineStr"/>
+      <c r="D44" s="16" t="inlineStr"/>
       <c r="E44" s="16" t="inlineStr">
         <is>
           <t>법인회원 운송비 등록/수정</t>
         </is>
       </c>
-      <c r="F44" s="15" t="inlineStr">
-        <is>
-          <t>법인회원별 운송비 할인율 설정</t>
+      <c r="F44" s="17" t="inlineStr">
+        <is>
+          <t>법인 또는 부서 단위로 AIR·SEA·CIR·CCL 서비스 할인율(%)과 영업이익율(%) 설정. 부서별로 다른 할인율 적용 가능.</t>
         </is>
       </c>
       <c r="G44" s="15" t="inlineStr">
@@ -1843,92 +1909,104 @@
       </c>
       <c r="I44" s="15" t="inlineStr"/>
     </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+    <row r="45" ht="23" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>오더관리</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr"/>
-      <c r="D45" s="5" t="inlineStr"/>
-      <c r="E45" s="5" t="inlineStr"/>
-      <c r="F45" s="5" t="inlineStr"/>
-      <c r="G45" s="5" t="inlineStr"/>
-      <c r="H45" s="17" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>화물 운송 의뢰 단위인 오더를 등록·관리하는 핵심 기능. 오더는 송하인·수하인·화물·서비스 정보로 구성.</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="18" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr"/>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr"/>
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>오더 기본관리</t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr"/>
-      <c r="E46" s="8" t="inlineStr"/>
-      <c r="F46" s="8" t="inlineStr"/>
-      <c r="G46" s="8" t="inlineStr"/>
-      <c r="H46" s="17" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr"/>
+      <c r="E46" s="7" t="inlineStr"/>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>오더의 신규 등록, 수정, 삭제, 조회를 처리.</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr"/>
+      <c r="H46" s="18" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I46" s="8" t="inlineStr"/>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>3.1.1</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr"/>
+      <c r="B47" s="10" t="inlineStr"/>
       <c r="C47" s="11" t="inlineStr"/>
-      <c r="D47" s="12" t="inlineStr">
+      <c r="D47" s="11" t="inlineStr">
         <is>
           <t>오더 등록</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr"/>
-      <c r="F47" s="11" t="inlineStr"/>
-      <c r="G47" s="11" t="inlineStr"/>
-      <c r="H47" s="18" t="inlineStr">
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>새 운송 오더를 시스템에 등록. 오더번호는 시스템이 자동 생성(예: ORD-20260415-00001). 초기 상태는 REGISTERED.</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="inlineStr"/>
+      <c r="H47" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I47" s="11" t="inlineStr"/>
-    </row>
-    <row r="48" ht="18" customHeight="1">
+      <c r="I47" s="10" t="inlineStr"/>
+    </row>
+    <row r="48" ht="26" customHeight="1">
       <c r="A48" s="14" t="inlineStr">
         <is>
           <t>3.1.1.1</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr"/>
-      <c r="C48" s="15" t="inlineStr"/>
-      <c r="D48" s="15" t="inlineStr"/>
+      <c r="C48" s="16" t="inlineStr"/>
+      <c r="D48" s="16" t="inlineStr"/>
       <c r="E48" s="16" t="inlineStr">
         <is>
           <t>송하인 정보 입력</t>
         </is>
       </c>
-      <c r="F48" s="15" t="inlineStr">
-        <is>
-          <t>발송자 이름/주소/전화번호 입력</t>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>화물을 보내는 송하인(발송자) 정보 입력. 이름·국가코드·우편번호·주소·상세주소·전화번호. 법인 송하인인 경우 사업자등록번호 추가 입력.</t>
         </is>
       </c>
       <c r="G48" s="15" t="inlineStr">
@@ -1936,30 +2014,30 @@
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H48" s="18" t="inlineStr">
+      <c r="H48" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
       <c r="I48" s="15" t="inlineStr"/>
     </row>
-    <row r="49" ht="18" customHeight="1">
+    <row r="49" ht="27" customHeight="1">
       <c r="A49" s="14" t="inlineStr">
         <is>
           <t>3.1.1.2</t>
         </is>
       </c>
       <c r="B49" s="15" t="inlineStr"/>
-      <c r="C49" s="15" t="inlineStr"/>
-      <c r="D49" s="15" t="inlineStr"/>
+      <c r="C49" s="16" t="inlineStr"/>
+      <c r="D49" s="16" t="inlineStr"/>
       <c r="E49" s="16" t="inlineStr">
         <is>
           <t>수하인 정보 입력</t>
         </is>
       </c>
-      <c r="F49" s="15" t="inlineStr">
-        <is>
-          <t>수취인 이름/주소/전화번호 입력</t>
+      <c r="F49" s="17" t="inlineStr">
+        <is>
+          <t>화물을 받는 수하인(수취인·수입자) 정보 입력. 이름·국가코드·우편번호·주소·상세주소·전화번호. 법인 수하인인 경우 사업자등록번호 추가 입력.</t>
         </is>
       </c>
       <c r="G49" s="15" t="inlineStr">
@@ -1967,30 +2045,30 @@
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H49" s="18" t="inlineStr">
+      <c r="H49" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
       <c r="I49" s="15" t="inlineStr"/>
     </row>
-    <row r="50" ht="18" customHeight="1">
+    <row r="50" ht="32" customHeight="1">
       <c r="A50" s="14" t="inlineStr">
         <is>
           <t>3.1.1.3</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr"/>
-      <c r="C50" s="15" t="inlineStr"/>
-      <c r="D50" s="15" t="inlineStr"/>
+      <c r="C50" s="16" t="inlineStr"/>
+      <c r="D50" s="16" t="inlineStr"/>
       <c r="E50" s="16" t="inlineStr">
         <is>
           <t>화물 정보 입력</t>
         </is>
       </c>
-      <c r="F50" s="15" t="inlineStr">
-        <is>
-          <t>품명/HS코드/원산지/수량/중량/CBM</t>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>운송 화물의 상세 정보 입력. 품명·HS코드·원산지(국가코드)·개별수량(PCS)·포장수량(CTNS/PKGS)·총중량(kg)·순중량(kg)·용적(CBM). 운송원가 계산에 총중량과 CBM이 사용됨.</t>
         </is>
       </c>
       <c r="G50" s="15" t="inlineStr">
@@ -1998,30 +2076,30 @@
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H50" s="18" t="inlineStr">
+      <c r="H50" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
       <c r="I50" s="15" t="inlineStr"/>
     </row>
-    <row r="51" ht="18" customHeight="1">
+    <row r="51" ht="34" customHeight="1">
       <c r="A51" s="14" t="inlineStr">
         <is>
           <t>3.1.1.4</t>
         </is>
       </c>
       <c r="B51" s="15" t="inlineStr"/>
-      <c r="C51" s="15" t="inlineStr"/>
-      <c r="D51" s="15" t="inlineStr"/>
+      <c r="C51" s="16" t="inlineStr"/>
+      <c r="D51" s="16" t="inlineStr"/>
       <c r="E51" s="16" t="inlineStr">
         <is>
           <t>특수화물 기재</t>
         </is>
       </c>
-      <c r="F51" s="15" t="inlineStr">
-        <is>
-          <t>위험물/냉동·냉장/고가품/중고품</t>
+      <c r="F51" s="17" t="inlineStr">
+        <is>
+          <t>일반화물 외 특수 취급이 필요한 항목 기재. ① 위험물: IMDG 위험물 코드 입력 ② 냉동·냉장: 보관 온도(℃) 입력 ③ 고가품: 단가 및 총액 입력 ④ 중고품(Used/Secondhand): 중고품 여부 표시.</t>
         </is>
       </c>
       <c r="G51" s="15" t="inlineStr">
@@ -2029,181 +2107,189 @@
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H51" s="18" t="inlineStr">
+      <c r="H51" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
       <c r="I51" s="15" t="inlineStr"/>
     </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="10" t="inlineStr">
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>3.1.2</t>
         </is>
       </c>
-      <c r="B52" s="11" t="inlineStr"/>
+      <c r="B52" s="10" t="inlineStr"/>
       <c r="C52" s="11" t="inlineStr"/>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="D52" s="11" t="inlineStr">
         <is>
           <t>오더 수정</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr"/>
-      <c r="F52" s="11" t="inlineStr">
-        <is>
-          <t>송하인·수하인·화물정보 수정 (입고 전까지)</t>
-        </is>
-      </c>
-      <c r="G52" s="11" t="inlineStr">
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>등록된 오더의 정보를 수정. 수정 가능 범위: 송하인·수하인·화물 정보 전체. 단, 오더가 Packing(마스터오더 포함)되었거나 '입고' 이후 처리 단계에서는 수정 불가.</t>
+        </is>
+      </c>
+      <c r="G52" s="10" t="inlineStr">
         <is>
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H52" s="18" t="inlineStr">
+      <c r="H52" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I52" s="11" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>입고 이후 수정 불가</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="10" t="inlineStr">
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>3.1.3</t>
         </is>
       </c>
-      <c r="B53" s="11" t="inlineStr"/>
+      <c r="B53" s="10" t="inlineStr"/>
       <c r="C53" s="11" t="inlineStr"/>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D53" s="11" t="inlineStr">
         <is>
           <t>오더 삭제</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr"/>
-      <c r="F53" s="11" t="inlineStr">
-        <is>
-          <t>오더 삭제 (Packing·입고 전까지)</t>
-        </is>
-      </c>
-      <c r="G53" s="11" t="inlineStr">
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>오더 조회 목록에서 선택하여 삭제. 삭제 시 송하인·수하인·화물 정보 전체 삭제. Packing 또는 입고 이후 단계의 오더는 삭제 불가.</t>
+        </is>
+      </c>
+      <c r="G53" s="10" t="inlineStr">
         <is>
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H53" s="18" t="inlineStr">
+      <c r="H53" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I53" s="11" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>입고 이후 삭제 불가</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="10" t="inlineStr">
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>3.1.4</t>
         </is>
       </c>
-      <c r="B54" s="11" t="inlineStr"/>
+      <c r="B54" s="10" t="inlineStr"/>
       <c r="C54" s="11" t="inlineStr"/>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="D54" s="11" t="inlineStr">
         <is>
           <t>오더 조회</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr"/>
-      <c r="F54" s="11" t="inlineStr">
-        <is>
-          <t>오더 목록 및 상세 조회</t>
-        </is>
-      </c>
-      <c r="G54" s="11" t="inlineStr">
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>오더 목록 조회 및 상세 조회. 조회 조건: 회원명·법인명·부서명·등록일자. 상세 조회 시 오더정보·송하인·수하인·화물·서비스 정보를 모두 확인 가능.</t>
+        </is>
+      </c>
+      <c r="G54" s="10" t="inlineStr">
         <is>
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H54" s="18" t="inlineStr">
+      <c r="H54" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I54" s="11" t="inlineStr"/>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="7" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr"/>
+    </row>
+    <row r="55" ht="25" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr"/>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr"/>
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>서비스 관리</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr"/>
-      <c r="E55" s="8" t="inlineStr"/>
-      <c r="F55" s="8" t="inlineStr"/>
-      <c r="G55" s="8" t="inlineStr"/>
-      <c r="H55" s="17" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr"/>
+      <c r="E55" s="7" t="inlineStr"/>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>오더에 운송 서비스(AIR·SEA·CIR·CCL)를 추가·수정·삭제하는 기능. 하나의 오더에 최대 4가지 서비스 추가 가능.</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr"/>
+      <c r="H55" s="18" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I55" s="8" t="inlineStr"/>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="10" t="inlineStr">
+      <c r="I55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56" ht="23" customHeight="1">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>3.2.1</t>
         </is>
       </c>
-      <c r="B56" s="11" t="inlineStr"/>
+      <c r="B56" s="10" t="inlineStr"/>
       <c r="C56" s="11" t="inlineStr"/>
-      <c r="D56" s="12" t="inlineStr">
+      <c r="D56" s="11" t="inlineStr">
         <is>
           <t>서비스 추가</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr"/>
-      <c r="F56" s="11" t="inlineStr"/>
-      <c r="G56" s="11" t="inlineStr"/>
-      <c r="H56" s="18" t="inlineStr">
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>오더에 운송 서비스를 추가. 서비스 구분코드(AIR/SEA/CIR/CCL)를 선택 후 세부 정보 입력.</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr"/>
+      <c r="H56" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I56" s="11" t="inlineStr">
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>최대 4개 서비스</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
+    <row r="57" ht="28" customHeight="1">
       <c r="A57" s="14" t="inlineStr">
         <is>
           <t>3.2.1.1</t>
         </is>
       </c>
       <c r="B57" s="15" t="inlineStr"/>
-      <c r="C57" s="15" t="inlineStr"/>
-      <c r="D57" s="15" t="inlineStr"/>
+      <c r="C57" s="16" t="inlineStr"/>
+      <c r="D57" s="16" t="inlineStr"/>
       <c r="E57" s="16" t="inlineStr">
         <is>
           <t>AIR(항운) 서비스 추가</t>
         </is>
       </c>
-      <c r="F57" s="15" t="inlineStr">
-        <is>
-          <t>출발국가·공항, 도착국가·공항, 항공사, 스케줄 선택</t>
+      <c r="F57" s="17" t="inlineStr">
+        <is>
+          <t>출발국가코드와 도착국가코드를 입력하여 항공운송수단 조회. 출발공항·도착공항·항공사·운항스케줄을 선택하면 서비스 등록 완료. 현재일 기준 운항 스케줄 자동 조회.</t>
         </is>
       </c>
       <c r="G57" s="15" t="inlineStr">
@@ -2211,30 +2297,30 @@
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H57" s="18" t="inlineStr">
+      <c r="H57" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
       <c r="I57" s="15" t="inlineStr"/>
     </row>
-    <row r="58" ht="18" customHeight="1">
+    <row r="58" ht="25" customHeight="1">
       <c r="A58" s="14" t="inlineStr">
         <is>
           <t>3.2.1.2</t>
         </is>
       </c>
       <c r="B58" s="15" t="inlineStr"/>
-      <c r="C58" s="15" t="inlineStr"/>
-      <c r="D58" s="15" t="inlineStr"/>
+      <c r="C58" s="16" t="inlineStr"/>
+      <c r="D58" s="16" t="inlineStr"/>
       <c r="E58" s="16" t="inlineStr">
         <is>
           <t>SEA(해운) 서비스 추가</t>
         </is>
       </c>
-      <c r="F58" s="15" t="inlineStr">
-        <is>
-          <t>출발국가·항구, 도착국가·항구, 선사, 스케줄 선택</t>
+      <c r="F58" s="17" t="inlineStr">
+        <is>
+          <t>출발국가코드와 도착국가코드를 입력하여 해운운송수단 조회. 출발항구·도착항구·선사·운항스케줄을 선택하면 서비스 등록 완료.</t>
         </is>
       </c>
       <c r="G58" s="15" t="inlineStr">
@@ -2242,30 +2328,30 @@
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H58" s="18" t="inlineStr">
+      <c r="H58" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
       <c r="I58" s="15" t="inlineStr"/>
     </row>
-    <row r="59" ht="18" customHeight="1">
+    <row r="59" ht="24" customHeight="1">
       <c r="A59" s="14" t="inlineStr">
         <is>
           <t>3.2.1.3</t>
         </is>
       </c>
       <c r="B59" s="15" t="inlineStr"/>
-      <c r="C59" s="15" t="inlineStr"/>
-      <c r="D59" s="15" t="inlineStr"/>
+      <c r="C59" s="16" t="inlineStr"/>
+      <c r="D59" s="16" t="inlineStr"/>
       <c r="E59" s="16" t="inlineStr">
         <is>
           <t>CIR(택배) 서비스 추가</t>
         </is>
       </c>
-      <c r="F59" s="15" t="inlineStr">
-        <is>
-          <t>도착국가로 택배사 선택, 운송장 출력</t>
+      <c r="F59" s="17" t="inlineStr">
+        <is>
+          <t>도착국가코드로 서비스 가능한 택배사 목록 조회 후 선택. 택배사 선택 완료 시 운송장 출력 가능 상태로 전환.</t>
         </is>
       </c>
       <c r="G59" s="15" t="inlineStr">
@@ -2273,30 +2359,30 @@
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H59" s="18" t="inlineStr">
+      <c r="H59" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
       <c r="I59" s="15" t="inlineStr"/>
     </row>
-    <row r="60" ht="18" customHeight="1">
+    <row r="60" ht="23" customHeight="1">
       <c r="A60" s="14" t="inlineStr">
         <is>
           <t>3.2.1.4</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr"/>
-      <c r="C60" s="15" t="inlineStr"/>
-      <c r="D60" s="15" t="inlineStr"/>
+      <c r="C60" s="16" t="inlineStr"/>
+      <c r="D60" s="16" t="inlineStr"/>
       <c r="E60" s="16" t="inlineStr">
         <is>
           <t>CCL(통관) 서비스 추가</t>
         </is>
       </c>
-      <c r="F60" s="15" t="inlineStr">
-        <is>
-          <t>도착국가로 통관사 선택</t>
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>도착국가코드로 서비스 가능한 통관사 목록 조회 후 선택. 통관 서비스는 별도 통관신고 처리와 연동.</t>
         </is>
       </c>
       <c r="G60" s="15" t="inlineStr">
@@ -2304,2512 +2390,2632 @@
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H60" s="18" t="inlineStr">
+      <c r="H60" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
       <c r="I60" s="15" t="inlineStr"/>
     </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="10" t="inlineStr">
+    <row r="61" ht="25" customHeight="1">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>3.2.2</t>
         </is>
       </c>
-      <c r="B61" s="11" t="inlineStr"/>
+      <c r="B61" s="10" t="inlineStr"/>
       <c r="C61" s="11" t="inlineStr"/>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="D61" s="11" t="inlineStr">
         <is>
           <t>서비스 수정</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr"/>
-      <c r="F61" s="11" t="inlineStr">
-        <is>
-          <t>등록된 서비스 정보 수정</t>
-        </is>
-      </c>
-      <c r="G61" s="11" t="inlineStr">
+      <c r="F61" s="12" t="inlineStr">
+        <is>
+          <t>등록된 서비스의 운송수단·스케줄 정보를 수정. 서비스 구분코드(AIR/SEA/CIR/CCL)는 변경 불가 — 삭제 후 재등록.</t>
+        </is>
+      </c>
+      <c r="G61" s="10" t="inlineStr">
         <is>
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H61" s="18" t="inlineStr">
+      <c r="H61" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I61" s="11" t="inlineStr"/>
-    </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="I61" s="10" t="inlineStr"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="9" t="inlineStr">
         <is>
           <t>3.2.3</t>
         </is>
       </c>
-      <c r="B62" s="11" t="inlineStr"/>
+      <c r="B62" s="10" t="inlineStr"/>
       <c r="C62" s="11" t="inlineStr"/>
-      <c r="D62" s="12" t="inlineStr">
+      <c r="D62" s="11" t="inlineStr">
         <is>
           <t>서비스 삭제</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr"/>
-      <c r="F62" s="11" t="inlineStr">
-        <is>
-          <t>등록된 서비스 삭제</t>
-        </is>
-      </c>
-      <c r="G62" s="11" t="inlineStr">
+      <c r="F62" s="12" t="inlineStr">
+        <is>
+          <t>오더에 등록된 서비스를 삭제. 입고 이후 처리 단계에서는 삭제 불가.</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="inlineStr">
         <is>
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H62" s="18" t="inlineStr">
+      <c r="H62" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I62" s="11" t="inlineStr"/>
-    </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="I62" s="10" t="inlineStr"/>
+    </row>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="9" t="inlineStr">
         <is>
           <t>3.2.4</t>
         </is>
       </c>
-      <c r="B63" s="11" t="inlineStr"/>
+      <c r="B63" s="10" t="inlineStr"/>
       <c r="C63" s="11" t="inlineStr"/>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="D63" s="11" t="inlineStr">
         <is>
           <t>운항스케줄 조회</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr"/>
-      <c r="F63" s="11" t="inlineStr">
-        <is>
-          <t>현재일 기준 운항 스케줄 조회 및 선택</t>
-        </is>
-      </c>
-      <c r="G63" s="11" t="inlineStr">
+      <c r="F63" s="12" t="inlineStr">
+        <is>
+          <t>AIR·SEA 서비스 추가 시 현재일 기준 운항 가능한 스케줄 목록 조회. 출발지·도착지·운송사 조건으로 필터링하여 원하는 스케줄 선택.</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="inlineStr">
         <is>
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H63" s="18" t="inlineStr">
+      <c r="H63" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I63" s="11" t="inlineStr"/>
-    </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="7" t="inlineStr">
+      <c r="I63" s="10" t="inlineStr"/>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr"/>
-      <c r="C64" s="9" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr"/>
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>운송비용 관리</t>
         </is>
       </c>
-      <c r="D64" s="8" t="inlineStr"/>
-      <c r="E64" s="8" t="inlineStr"/>
-      <c r="F64" s="8" t="inlineStr"/>
-      <c r="G64" s="8" t="inlineStr"/>
-      <c r="H64" s="17" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr"/>
+      <c r="E64" s="7" t="inlineStr"/>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>오더별 서비스 운송비용을 자동 계산하고 Extra Charge를 관리.</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr"/>
+      <c r="H64" s="18" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I64" s="8" t="inlineStr"/>
-    </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="10" t="inlineStr">
+      <c r="I64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65" ht="31" customHeight="1">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>3.3.1</t>
         </is>
       </c>
-      <c r="B65" s="11" t="inlineStr"/>
+      <c r="B65" s="10" t="inlineStr"/>
       <c r="C65" s="11" t="inlineStr"/>
-      <c r="D65" s="12" t="inlineStr">
+      <c r="D65" s="11" t="inlineStr">
         <is>
           <t>운송비용 자동 계산</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr"/>
-      <c r="F65" s="11" t="inlineStr">
-        <is>
-          <t>원가+이익율+할인율 적용하여 자동 계산</t>
-        </is>
-      </c>
-      <c r="G65" s="11" t="inlineStr">
+      <c r="F65" s="12" t="inlineStr">
+        <is>
+          <t>화물 총중량·CBM 기반으로 운송원가 산출 후 영업이익율과 회원할인율 적용하여 운송비 자동 계산. 계산식: 운송비 = 원가 + (원가 × 영업이익율%) − (원가 × (1 − 할인율%))</t>
+        </is>
+      </c>
+      <c r="G65" s="10" t="inlineStr">
         <is>
           <t>시스템</t>
         </is>
       </c>
-      <c r="H65" s="18" t="inlineStr">
+      <c r="H65" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I65" s="11" t="inlineStr"/>
-    </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="I65" s="10" t="inlineStr"/>
+    </row>
+    <row r="66" ht="35" customHeight="1">
+      <c r="A66" s="9" t="inlineStr">
         <is>
           <t>3.3.2</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr"/>
+      <c r="B66" s="10" t="inlineStr"/>
       <c r="C66" s="11" t="inlineStr"/>
-      <c r="D66" s="12" t="inlineStr">
+      <c r="D66" s="11" t="inlineStr">
         <is>
           <t>Extra Charge 입력</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr"/>
-      <c r="F66" s="11" t="inlineStr">
-        <is>
-          <t>오더별 추가비용 수동 입력 (소수점 1자리)</t>
-        </is>
-      </c>
-      <c r="G66" s="11" t="inlineStr">
+      <c r="F66" s="12" t="inlineStr">
+        <is>
+          <t>오더별 추가 비용(Extra Charge)을 수동 입력. 소수점 1자리까지 입력 가능(예: 15.5). 입력 권한: 회원·운영자는 Extra Charge만 수정 가능, 관리자는 운송원가·운송비·Extra Charge 모두 수정 가능.</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="inlineStr">
         <is>
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H66" s="18" t="inlineStr">
+      <c r="H66" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I66" s="11" t="inlineStr"/>
-    </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="10" t="inlineStr">
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>소수점 1자리</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="26" customHeight="1">
+      <c r="A67" s="9" t="inlineStr">
         <is>
           <t>3.3.3</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr"/>
+      <c r="B67" s="10" t="inlineStr"/>
       <c r="C67" s="11" t="inlineStr"/>
-      <c r="D67" s="12" t="inlineStr">
+      <c r="D67" s="11" t="inlineStr">
         <is>
           <t>운송비용 조회</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr"/>
-      <c r="F67" s="11" t="inlineStr">
-        <is>
-          <t>서비스별 운송원가/운송비/Extra Charge 조회</t>
-        </is>
-      </c>
-      <c r="G67" s="11" t="inlineStr">
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>서비스별 운송원가·운송비·Extra Charge 조회. 회원은 운송비·Extra Charge만 조회, 관리자는 원가 포함 전체 조회.</t>
+        </is>
+      </c>
+      <c r="G67" s="10" t="inlineStr">
         <is>
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H67" s="18" t="inlineStr">
+      <c r="H67" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I67" s="11" t="inlineStr"/>
-    </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="I67" s="10" t="inlineStr"/>
+    </row>
+    <row r="68" ht="26" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>마스터오더관리</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr"/>
-      <c r="D68" s="5" t="inlineStr"/>
-      <c r="E68" s="5" t="inlineStr"/>
-      <c r="F68" s="5" t="inlineStr"/>
-      <c r="G68" s="5" t="inlineStr"/>
-      <c r="H68" s="17" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr"/>
+      <c r="D68" s="3" t="inlineStr"/>
+      <c r="E68" s="3" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>여러 오더를 하나의 마스터오더로 묶어 일괄 운송 처리. 마스터오더 번호는 시스템 자동 생성(예: MO-20260415-00001).</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="18" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I68" s="5" t="inlineStr"/>
-    </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="7" t="inlineStr">
+      <c r="I68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69" ht="26" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr"/>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="B69" s="7" t="inlineStr"/>
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>마스터오더 등록</t>
         </is>
       </c>
-      <c r="D69" s="8" t="inlineStr"/>
-      <c r="E69" s="8" t="inlineStr"/>
+      <c r="D69" s="7" t="inlineStr"/>
+      <c r="E69" s="7" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>마스터오더 번호 자동 생성</t>
-        </is>
-      </c>
-      <c r="G69" s="8" t="inlineStr">
+          <t>마스터오더를 신규 생성. 초기 상태는 CREATED. 생성 시 마스터오더번호가 자동 부여되며 이후 오더를 Packing하여 추가.</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H69" s="17" t="inlineStr">
+      <c r="H69" s="18" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I69" s="8" t="inlineStr"/>
-    </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="7" t="inlineStr">
+      <c r="I69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70" ht="26" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr"/>
-      <c r="C70" s="9" t="inlineStr">
+      <c r="B70" s="7" t="inlineStr"/>
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>오더 Packing</t>
         </is>
       </c>
-      <c r="D70" s="8" t="inlineStr"/>
-      <c r="E70" s="8" t="inlineStr"/>
+      <c r="D70" s="7" t="inlineStr"/>
+      <c r="E70" s="7" t="inlineStr"/>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>여러 오더를 마스터오더에 포함</t>
-        </is>
-      </c>
-      <c r="G70" s="8" t="inlineStr">
+          <t>등록된 오더를 마스터오더에 포함. Packing된 오더는 단독 수정·삭제 불가. 마스터오더 단위로 창고 입고·출고·Tracking 처리.</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H70" s="17" t="inlineStr">
+      <c r="H70" s="18" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I70" s="8" t="inlineStr"/>
-    </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="7" t="inlineStr">
+      <c r="I70" s="7" t="inlineStr"/>
+    </row>
+    <row r="71" ht="21" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr"/>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr"/>
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>마스터오더 수정</t>
         </is>
       </c>
-      <c r="D71" s="8" t="inlineStr"/>
-      <c r="E71" s="8" t="inlineStr"/>
+      <c r="D71" s="7" t="inlineStr"/>
+      <c r="E71" s="7" t="inlineStr"/>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>마스터오더 정보 수정</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="inlineStr">
+          <t>마스터오더 상태 및 포함된 오더 구성 수정. 입고 이후 처리 단계에서는 수정 불가.</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H71" s="17" t="inlineStr">
+      <c r="H71" s="18" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I71" s="8" t="inlineStr"/>
-    </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="7" t="inlineStr">
+      <c r="I71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72" ht="26" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr"/>
-      <c r="C72" s="9" t="inlineStr">
+      <c r="B72" s="7" t="inlineStr"/>
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>마스터오더 삭제</t>
         </is>
       </c>
-      <c r="D72" s="8" t="inlineStr"/>
-      <c r="E72" s="8" t="inlineStr"/>
+      <c r="D72" s="7" t="inlineStr"/>
+      <c r="E72" s="7" t="inlineStr"/>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>마스터오더 삭제</t>
-        </is>
-      </c>
-      <c r="G72" s="8" t="inlineStr">
+          <t>마스터오더 삭제. 입고 전 단계에서만 삭제 가능. 삭제 시 포함된 오더의 master_order_id를 Null 처리하여 오더는 유지.</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H72" s="17" t="inlineStr">
+      <c r="H72" s="18" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I72" s="8" t="inlineStr"/>
-    </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="7" t="inlineStr">
+      <c r="I72" s="7" t="inlineStr"/>
+    </row>
+    <row r="73" ht="25" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr"/>
-      <c r="C73" s="9" t="inlineStr">
+      <c r="B73" s="7" t="inlineStr"/>
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>마스터오더 조회</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr"/>
-      <c r="E73" s="8" t="inlineStr"/>
+      <c r="D73" s="7" t="inlineStr"/>
+      <c r="E73" s="7" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>마스터오더 목록 및 상세 조회</t>
-        </is>
-      </c>
-      <c r="G73" s="8" t="inlineStr">
+          <t>마스터오더 목록 및 상세 조회. 상세 조회 시 포함된 오더 목록, 서비스 정보, Tracking 현황을 함께 확인 가능.</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
         <is>
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H73" s="17" t="inlineStr">
+      <c r="H73" s="18" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I73" s="8" t="inlineStr"/>
-    </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="I73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74" ht="25" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>창고관리</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr"/>
-      <c r="D74" s="5" t="inlineStr"/>
-      <c r="E74" s="5" t="inlineStr"/>
-      <c r="F74" s="5" t="inlineStr"/>
-      <c r="G74" s="5" t="inlineStr"/>
-      <c r="H74" s="17" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr"/>
+      <c r="D74" s="3" t="inlineStr"/>
+      <c r="E74" s="3" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>물류 창고에서의 화물 입고·출고 처리 및 운송장 출력 기능. 1차 개발은 WEB, 2차 개발에서 PDA/App 지원 예정.</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr"/>
+      <c r="H74" s="18" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I74" s="5" t="inlineStr"/>
-    </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="7" t="inlineStr">
+      <c r="I74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75" ht="19" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr"/>
-      <c r="C75" s="9" t="inlineStr">
+      <c r="B75" s="7" t="inlineStr"/>
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>입고 관리</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr"/>
-      <c r="E75" s="8" t="inlineStr"/>
-      <c r="F75" s="8" t="inlineStr"/>
-      <c r="G75" s="8" t="inlineStr"/>
-      <c r="H75" s="17" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr"/>
+      <c r="E75" s="7" t="inlineStr"/>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>화물이 창고에 도착하여 수령 확인 후 입고 처리하는 기능.</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr"/>
+      <c r="H75" s="18" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I75" s="8" t="inlineStr"/>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="10" t="inlineStr">
+      <c r="I75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76" ht="29" customHeight="1">
+      <c r="A76" s="9" t="inlineStr">
         <is>
           <t>5.1.1</t>
         </is>
       </c>
-      <c r="B76" s="11" t="inlineStr"/>
+      <c r="B76" s="10" t="inlineStr"/>
       <c r="C76" s="11" t="inlineStr"/>
-      <c r="D76" s="12" t="inlineStr">
+      <c r="D76" s="11" t="inlineStr">
         <is>
           <t>입고 처리</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr"/>
-      <c r="F76" s="11" t="inlineStr">
-        <is>
-          <t>오더 입고 처리 (WEB)</t>
-        </is>
-      </c>
-      <c r="G76" s="11" t="inlineStr">
+      <c r="F76" s="12" t="inlineStr">
+        <is>
+          <t>오더를 선택하여 입고 처리. 입고 완료 시 오더 상태가 WAREHOUSED로 변경. 입고 이후에는 오더 수정·삭제 불가. 입고 담당자명과 입고일시가 자동 기록됨.</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H76" s="18" t="inlineStr">
+      <c r="H76" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I76" s="11" t="inlineStr">
+      <c r="I76" s="10" t="inlineStr">
         <is>
           <t>1차 WEB, 2차 PDA</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="10" t="inlineStr">
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="9" t="inlineStr">
         <is>
           <t>5.1.2</t>
         </is>
       </c>
-      <c r="B77" s="11" t="inlineStr"/>
+      <c r="B77" s="10" t="inlineStr"/>
       <c r="C77" s="11" t="inlineStr"/>
-      <c r="D77" s="12" t="inlineStr">
+      <c r="D77" s="11" t="inlineStr">
         <is>
           <t>입고 조회</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr"/>
-      <c r="F77" s="11" t="inlineStr">
-        <is>
-          <t>입고 이력 조회</t>
-        </is>
-      </c>
-      <c r="G77" s="11" t="inlineStr">
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>입고 처리된 오더 목록 및 이력 조회. 오더번호·날짜 기준 검색.</t>
+        </is>
+      </c>
+      <c r="G77" s="10" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H77" s="18" t="inlineStr">
+      <c r="H77" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I77" s="11" t="inlineStr"/>
-    </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="7" t="inlineStr">
+      <c r="I77" s="10" t="inlineStr"/>
+    </row>
+    <row r="78" ht="19" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr"/>
-      <c r="C78" s="9" t="inlineStr">
+      <c r="B78" s="7" t="inlineStr"/>
+      <c r="C78" s="7" t="inlineStr">
         <is>
           <t>출고 관리</t>
         </is>
       </c>
-      <c r="D78" s="8" t="inlineStr"/>
-      <c r="E78" s="8" t="inlineStr"/>
-      <c r="F78" s="8" t="inlineStr"/>
-      <c r="G78" s="8" t="inlineStr"/>
-      <c r="H78" s="17" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr"/>
+      <c r="E78" s="7" t="inlineStr"/>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>창고에서 화물을 출고하고 운송장을 출력·부착하는 기능.</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr"/>
+      <c r="H78" s="18" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I78" s="8" t="inlineStr"/>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="10" t="inlineStr">
+      <c r="I78" s="7" t="inlineStr"/>
+    </row>
+    <row r="79" ht="23" customHeight="1">
+      <c r="A79" s="9" t="inlineStr">
         <is>
           <t>5.2.1</t>
         </is>
       </c>
-      <c r="B79" s="11" t="inlineStr"/>
+      <c r="B79" s="10" t="inlineStr"/>
       <c r="C79" s="11" t="inlineStr"/>
-      <c r="D79" s="12" t="inlineStr">
+      <c r="D79" s="11" t="inlineStr">
         <is>
           <t>바코드 스캔</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr"/>
-      <c r="F79" s="11" t="inlineStr">
-        <is>
-          <t>바코드로 오더 식별 및 출고처리</t>
-        </is>
-      </c>
-      <c r="G79" s="11" t="inlineStr">
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>웹캠 또는 스캐너로 바코드를 스캔하여 오더를 식별. 스캔된 오더번호를 기반으로 운송장 출력 및 출고 처리.</t>
+        </is>
+      </c>
+      <c r="G79" s="10" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H79" s="18" t="inlineStr">
+      <c r="H79" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I79" s="11" t="inlineStr">
+      <c r="I79" s="10" t="inlineStr">
         <is>
           <t>WEB 스캔</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="10" t="inlineStr">
+    <row r="80" ht="25" customHeight="1">
+      <c r="A80" s="9" t="inlineStr">
         <is>
           <t>5.2.2</t>
         </is>
       </c>
-      <c r="B80" s="11" t="inlineStr"/>
+      <c r="B80" s="10" t="inlineStr"/>
       <c r="C80" s="11" t="inlineStr"/>
-      <c r="D80" s="12" t="inlineStr">
+      <c r="D80" s="11" t="inlineStr">
         <is>
           <t>운송장 출력</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr"/>
-      <c r="F80" s="11" t="inlineStr">
-        <is>
-          <t>운송장 생성 및 출력</t>
-        </is>
-      </c>
-      <c r="G80" s="11" t="inlineStr">
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>CIR(택배) 서비스 오더의 운송장을 PDF로 생성 및 출력. 마스터오더에 포함된 오더 정보를 기반으로 운송장 내용 자동 구성.</t>
+        </is>
+      </c>
+      <c r="G80" s="10" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H80" s="18" t="inlineStr">
+      <c r="H80" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I80" s="11" t="inlineStr"/>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="10" t="inlineStr">
+      <c r="I80" s="10" t="inlineStr"/>
+    </row>
+    <row r="81" ht="26" customHeight="1">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>5.2.3</t>
         </is>
       </c>
-      <c r="B81" s="11" t="inlineStr"/>
+      <c r="B81" s="10" t="inlineStr"/>
       <c r="C81" s="11" t="inlineStr"/>
-      <c r="D81" s="12" t="inlineStr">
+      <c r="D81" s="11" t="inlineStr">
         <is>
           <t>출고 처리</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr"/>
-      <c r="F81" s="11" t="inlineStr">
-        <is>
-          <t>운송장 부착 후 출고 확정</t>
-        </is>
-      </c>
-      <c r="G81" s="11" t="inlineStr">
+      <c r="F81" s="12" t="inlineStr">
+        <is>
+          <t>운송장 부착 확인 후 출고 처리. 출고 완료 시 오더 상태가 RELEASED로 변경. 출고 담당자명·운송장번호·출고일시 자동 기록.</t>
+        </is>
+      </c>
+      <c r="G81" s="10" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H81" s="18" t="inlineStr">
+      <c r="H81" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I81" s="11" t="inlineStr"/>
-    </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="10" t="inlineStr">
+      <c r="I81" s="10" t="inlineStr"/>
+    </row>
+    <row r="82" ht="21" customHeight="1">
+      <c r="A82" s="9" t="inlineStr">
         <is>
           <t>5.2.4</t>
         </is>
       </c>
-      <c r="B82" s="11" t="inlineStr"/>
+      <c r="B82" s="10" t="inlineStr"/>
       <c r="C82" s="11" t="inlineStr"/>
-      <c r="D82" s="12" t="inlineStr">
+      <c r="D82" s="11" t="inlineStr">
         <is>
           <t>출고 조회</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr"/>
-      <c r="F82" s="11" t="inlineStr">
-        <is>
-          <t>출고 이력 조회</t>
-        </is>
-      </c>
-      <c r="G82" s="11" t="inlineStr">
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>출고 처리된 오더 목록 및 이력 조회. 날짜·오더번호·운송장번호 기준 검색.</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H82" s="18" t="inlineStr">
+      <c r="H82" s="19" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="I82" s="11" t="inlineStr"/>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="3" t="inlineStr">
+      <c r="I82" s="10" t="inlineStr"/>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>운송 Tracking</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr"/>
-      <c r="D83" s="5" t="inlineStr"/>
-      <c r="E83" s="5" t="inlineStr"/>
-      <c r="F83" s="5" t="inlineStr"/>
-      <c r="G83" s="5" t="inlineStr"/>
-      <c r="H83" s="19" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr"/>
+      <c r="D83" s="3" t="inlineStr"/>
+      <c r="E83" s="3" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>항운(AIR)·해운(SEA)·택배(CIR) 운송 현황 및 통관 신고 결과를 조회하는 기능.</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr"/>
+      <c r="H83" s="20" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I83" s="5" t="inlineStr"/>
-    </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="7" t="inlineStr">
+      <c r="I83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84" ht="17" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr"/>
-      <c r="C84" s="9" t="inlineStr">
+      <c r="B84" s="7" t="inlineStr"/>
+      <c r="C84" s="7" t="inlineStr">
         <is>
           <t>항운(AIR) Tracking</t>
         </is>
       </c>
-      <c r="D84" s="8" t="inlineStr"/>
-      <c r="E84" s="8" t="inlineStr"/>
-      <c r="F84" s="8" t="inlineStr"/>
-      <c r="G84" s="8" t="inlineStr"/>
-      <c r="H84" s="19" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr"/>
+      <c r="E84" s="7" t="inlineStr"/>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>항공 화물의 실시간 운송 현황을 추적.</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr"/>
+      <c r="H84" s="20" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I84" s="8" t="inlineStr"/>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="10" t="inlineStr">
+      <c r="I84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="9" t="inlineStr">
         <is>
           <t>6.1.1</t>
         </is>
       </c>
-      <c r="B85" s="11" t="inlineStr"/>
+      <c r="B85" s="10" t="inlineStr"/>
       <c r="C85" s="11" t="inlineStr"/>
-      <c r="D85" s="12" t="inlineStr">
+      <c r="D85" s="11" t="inlineStr">
         <is>
           <t>Tracking 정보 조회</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr"/>
-      <c r="F85" s="11" t="inlineStr">
-        <is>
-          <t>항공 화물 운송 현황 조회</t>
-        </is>
-      </c>
-      <c r="G85" s="11" t="inlineStr">
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>오더별 항공 화물 Tracking 번호·상태·현재위치·최종갱신일시를 조회. 상태 예: Booked → Departed → In Transit → Arrived → Delivered</t>
+        </is>
+      </c>
+      <c r="G85" s="10" t="inlineStr">
         <is>
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H85" s="20" t="inlineStr">
+      <c r="H85" s="21" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I85" s="11" t="inlineStr"/>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="10" t="inlineStr">
+      <c r="I85" s="10" t="inlineStr"/>
+    </row>
+    <row r="86" ht="29" customHeight="1">
+      <c r="A86" s="9" t="inlineStr">
         <is>
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B86" s="11" t="inlineStr"/>
+      <c r="B86" s="10" t="inlineStr"/>
       <c r="C86" s="11" t="inlineStr"/>
-      <c r="D86" s="12" t="inlineStr">
+      <c r="D86" s="11" t="inlineStr">
         <is>
           <t>Tracking 정보 갱신</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr"/>
-      <c r="F86" s="11" t="inlineStr">
-        <is>
-          <t>오더별 최신 항운 Tracking 정보 갱신</t>
-        </is>
-      </c>
-      <c r="G86" s="11" t="inlineStr">
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>외부 항공사 Tracking API를 호출하여 최신 운송 상태를 업데이트. 자동 갱신(배치) 및 수동 갱신 모두 지원. API 응답 원본을 raw_data에 저장.</t>
+        </is>
+      </c>
+      <c r="G86" s="10" t="inlineStr">
         <is>
           <t>시스템/관리자</t>
         </is>
       </c>
-      <c r="H86" s="20" t="inlineStr">
+      <c r="H86" s="21" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I86" s="11" t="inlineStr"/>
-    </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="7" t="inlineStr">
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>외부 API 추후 확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="17" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr"/>
-      <c r="C87" s="9" t="inlineStr">
+      <c r="B87" s="7" t="inlineStr"/>
+      <c r="C87" s="7" t="inlineStr">
         <is>
           <t>해운(SEA) Tracking</t>
         </is>
       </c>
-      <c r="D87" s="8" t="inlineStr"/>
-      <c r="E87" s="8" t="inlineStr"/>
-      <c r="F87" s="8" t="inlineStr"/>
-      <c r="G87" s="8" t="inlineStr"/>
-      <c r="H87" s="19" t="inlineStr">
+      <c r="D87" s="7" t="inlineStr"/>
+      <c r="E87" s="7" t="inlineStr"/>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>해운 화물의 선박 운송 현황을 추적.</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr"/>
+      <c r="H87" s="20" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I87" s="8" t="inlineStr"/>
-    </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="10" t="inlineStr">
+      <c r="I87" s="7" t="inlineStr"/>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="9" t="inlineStr">
         <is>
           <t>6.2.1</t>
         </is>
       </c>
-      <c r="B88" s="11" t="inlineStr"/>
+      <c r="B88" s="10" t="inlineStr"/>
       <c r="C88" s="11" t="inlineStr"/>
-      <c r="D88" s="12" t="inlineStr">
+      <c r="D88" s="11" t="inlineStr">
         <is>
           <t>Tracking 정보 조회</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr"/>
-      <c r="F88" s="11" t="inlineStr">
-        <is>
-          <t>해운 화물 운송 현황 조회</t>
-        </is>
-      </c>
-      <c r="G88" s="11" t="inlineStr">
+      <c r="F88" s="12" t="inlineStr">
+        <is>
+          <t>오더별 해운 Tracking 번호(B/L번호)·상태·현재위치·최종갱신일시 조회. 상태 예: Loaded → Departed → On Board → Arrived → Unloaded</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr">
         <is>
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H88" s="20" t="inlineStr">
+      <c r="H88" s="21" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I88" s="11" t="inlineStr"/>
-    </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="10" t="inlineStr">
+      <c r="I88" s="10" t="inlineStr"/>
+    </row>
+    <row r="89" ht="24" customHeight="1">
+      <c r="A89" s="9" t="inlineStr">
         <is>
           <t>6.2.2</t>
         </is>
       </c>
-      <c r="B89" s="11" t="inlineStr"/>
+      <c r="B89" s="10" t="inlineStr"/>
       <c r="C89" s="11" t="inlineStr"/>
-      <c r="D89" s="12" t="inlineStr">
+      <c r="D89" s="11" t="inlineStr">
         <is>
           <t>Tracking 정보 갱신</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr"/>
-      <c r="F89" s="11" t="inlineStr">
-        <is>
-          <t>오더별 최신 해운 Tracking 정보 갱신</t>
-        </is>
-      </c>
-      <c r="G89" s="11" t="inlineStr">
+      <c r="F89" s="12" t="inlineStr">
+        <is>
+          <t>외부 선사 Tracking API를 호출하여 최신 운송 상태 업데이트. 자동 갱신(배치) 및 수동 갱신 지원.</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="inlineStr">
         <is>
           <t>시스템/관리자</t>
         </is>
       </c>
-      <c r="H89" s="20" t="inlineStr">
+      <c r="H89" s="21" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I89" s="11" t="inlineStr"/>
-    </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="7" t="inlineStr">
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>외부 API 추후 확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr"/>
-      <c r="C90" s="9" t="inlineStr">
+      <c r="B90" s="7" t="inlineStr"/>
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>택배(CIR) Tracking</t>
         </is>
       </c>
-      <c r="D90" s="8" t="inlineStr"/>
-      <c r="E90" s="8" t="inlineStr"/>
-      <c r="F90" s="8" t="inlineStr"/>
-      <c r="G90" s="8" t="inlineStr"/>
-      <c r="H90" s="19" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr"/>
+      <c r="E90" s="7" t="inlineStr"/>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>국제 택배 운송 현황을 추적.</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr"/>
+      <c r="H90" s="20" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I90" s="8" t="inlineStr"/>
-    </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="10" t="inlineStr">
+      <c r="I90" s="7" t="inlineStr"/>
+    </row>
+    <row r="91" ht="19" customHeight="1">
+      <c r="A91" s="9" t="inlineStr">
         <is>
           <t>6.3.1</t>
         </is>
       </c>
-      <c r="B91" s="11" t="inlineStr"/>
+      <c r="B91" s="10" t="inlineStr"/>
       <c r="C91" s="11" t="inlineStr"/>
-      <c r="D91" s="12" t="inlineStr">
+      <c r="D91" s="11" t="inlineStr">
         <is>
           <t>Tracking 정보 조회</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr"/>
-      <c r="F91" s="11" t="inlineStr">
-        <is>
-          <t>택배 운송 현황 조회</t>
-        </is>
-      </c>
-      <c r="G91" s="11" t="inlineStr">
+      <c r="F91" s="12" t="inlineStr">
+        <is>
+          <t>오더별 택배 운송장번호·상태·현재위치·최종갱신일시 조회.</t>
+        </is>
+      </c>
+      <c r="G91" s="10" t="inlineStr">
         <is>
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H91" s="20" t="inlineStr">
+      <c r="H91" s="21" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I91" s="11" t="inlineStr"/>
-    </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="10" t="inlineStr">
+      <c r="I91" s="10" t="inlineStr"/>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="9" t="inlineStr">
         <is>
           <t>6.3.2</t>
         </is>
       </c>
-      <c r="B92" s="11" t="inlineStr"/>
+      <c r="B92" s="10" t="inlineStr"/>
       <c r="C92" s="11" t="inlineStr"/>
-      <c r="D92" s="12" t="inlineStr">
+      <c r="D92" s="11" t="inlineStr">
         <is>
           <t>Tracking 정보 갱신</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr"/>
-      <c r="F92" s="11" t="inlineStr">
-        <is>
-          <t>오더별 최신 택배 Tracking 정보 갱신</t>
-        </is>
-      </c>
-      <c r="G92" s="11" t="inlineStr">
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>택배사 Tracking API를 호출하여 최신 배송 상태 업데이트.</t>
+        </is>
+      </c>
+      <c r="G92" s="10" t="inlineStr">
         <is>
           <t>시스템/관리자</t>
         </is>
       </c>
-      <c r="H92" s="20" t="inlineStr">
+      <c r="H92" s="21" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I92" s="11" t="inlineStr"/>
+      <c r="I92" s="10" t="inlineStr">
+        <is>
+          <t>외부 API 추후 확정</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="7" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr"/>
-      <c r="C93" s="9" t="inlineStr">
+      <c r="B93" s="7" t="inlineStr"/>
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>통관신고 관리</t>
         </is>
       </c>
-      <c r="D93" s="8" t="inlineStr"/>
-      <c r="E93" s="8" t="inlineStr"/>
-      <c r="F93" s="8" t="inlineStr"/>
-      <c r="G93" s="8" t="inlineStr"/>
-      <c r="H93" s="19" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr"/>
+      <c r="E93" s="7" t="inlineStr"/>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>통관(CCL) 서비스 연계 통관 신고 및 결과 관리.</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr"/>
+      <c r="H93" s="20" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I93" s="8" t="inlineStr"/>
-    </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="10" t="inlineStr">
+      <c r="I93" s="7" t="inlineStr"/>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="9" t="inlineStr">
         <is>
           <t>6.4.1</t>
         </is>
       </c>
-      <c r="B94" s="11" t="inlineStr"/>
+      <c r="B94" s="10" t="inlineStr"/>
       <c r="C94" s="11" t="inlineStr"/>
-      <c r="D94" s="12" t="inlineStr">
+      <c r="D94" s="11" t="inlineStr">
         <is>
           <t>통관신고 결과 조회</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr"/>
-      <c r="F94" s="11" t="inlineStr">
-        <is>
-          <t>통관 신고 번호·상태 조회</t>
-        </is>
-      </c>
-      <c r="G94" s="11" t="inlineStr">
+      <c r="F94" s="12" t="inlineStr">
+        <is>
+          <t>통관 신고번호·신고상태·신고일시·결과수신일시를 조회. 통관 완료 여부를 오더 단위로 확인 가능.</t>
+        </is>
+      </c>
+      <c r="G94" s="10" t="inlineStr">
         <is>
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H94" s="20" t="inlineStr">
+      <c r="H94" s="21" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I94" s="11" t="inlineStr"/>
-    </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="10" t="inlineStr">
+      <c r="I94" s="10" t="inlineStr"/>
+    </row>
+    <row r="95" ht="25" customHeight="1">
+      <c r="A95" s="9" t="inlineStr">
         <is>
           <t>6.4.2</t>
         </is>
       </c>
-      <c r="B95" s="11" t="inlineStr"/>
+      <c r="B95" s="10" t="inlineStr"/>
       <c r="C95" s="11" t="inlineStr"/>
-      <c r="D95" s="12" t="inlineStr">
+      <c r="D95" s="11" t="inlineStr">
         <is>
           <t>마스터오더 Tracking</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr"/>
-      <c r="F95" s="11" t="inlineStr">
-        <is>
-          <t>마스터오더에 포함된 오더 일괄 Tracking 갱신</t>
-        </is>
-      </c>
-      <c r="G95" s="11" t="inlineStr">
+      <c r="F95" s="12" t="inlineStr">
+        <is>
+          <t>마스터오더에 포함된 전체 오더의 Tracking 정보를 일괄 갱신. 마스터오더 단위로 전체 운송 현황을 한 화면에서 확인.</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H95" s="20" t="inlineStr">
+      <c r="H95" s="21" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I95" s="11" t="inlineStr"/>
-    </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="3" t="inlineStr">
+      <c r="I95" s="10" t="inlineStr"/>
+    </row>
+    <row r="96" ht="21" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t>회계/청구</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr"/>
-      <c r="D96" s="5" t="inlineStr"/>
-      <c r="E96" s="5" t="inlineStr"/>
-      <c r="F96" s="5" t="inlineStr"/>
-      <c r="G96" s="5" t="inlineStr"/>
-      <c r="H96" s="19" t="inlineStr">
+      <c r="C96" s="3" t="inlineStr"/>
+      <c r="D96" s="3" t="inlineStr"/>
+      <c r="E96" s="3" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>운송 서비스에 대한 청구서 발행·입금 확인·비용 관리·세금계산서 발행을 처리.</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr"/>
+      <c r="H96" s="20" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I96" s="5" t="inlineStr"/>
-    </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="7" t="inlineStr">
+      <c r="I96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97" ht="19" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr"/>
-      <c r="C97" s="9" t="inlineStr">
+      <c r="B97" s="7" t="inlineStr"/>
+      <c r="C97" s="7" t="inlineStr">
         <is>
           <t>청구서 관리</t>
         </is>
       </c>
-      <c r="D97" s="8" t="inlineStr"/>
-      <c r="E97" s="8" t="inlineStr"/>
-      <c r="F97" s="8" t="inlineStr"/>
-      <c r="G97" s="8" t="inlineStr"/>
-      <c r="H97" s="19" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr"/>
+      <c r="E97" s="7" t="inlineStr"/>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>오더·서비스별 운송비용을 집계하여 회원에게 청구서를 발행.</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr"/>
+      <c r="H97" s="20" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I97" s="8" t="inlineStr"/>
-    </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="10" t="inlineStr">
+      <c r="I97" s="7" t="inlineStr"/>
+    </row>
+    <row r="98" ht="29" customHeight="1">
+      <c r="A98" s="9" t="inlineStr">
         <is>
           <t>7.1.1</t>
         </is>
       </c>
-      <c r="B98" s="11" t="inlineStr"/>
+      <c r="B98" s="10" t="inlineStr"/>
       <c r="C98" s="11" t="inlineStr"/>
-      <c r="D98" s="12" t="inlineStr">
+      <c r="D98" s="11" t="inlineStr">
         <is>
           <t>청구서 생성</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr"/>
-      <c r="F98" s="11" t="inlineStr">
-        <is>
-          <t>회원별·기간별·운송수단별 청구서 생성</t>
-        </is>
-      </c>
-      <c r="G98" s="11" t="inlineStr">
+      <c r="F98" s="12" t="inlineStr">
+        <is>
+          <t>회원별·기간별·운송수단별 조건으로 청구 대상 오더를 집계하여 청구서 생성. 청구서번호 자동 생성(예: INV-20260415-00001). 초기 상태는 UNPAID.</t>
+        </is>
+      </c>
+      <c r="G98" s="10" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H98" s="20" t="inlineStr">
+      <c r="H98" s="21" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I98" s="11" t="inlineStr"/>
-    </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="10" t="inlineStr">
+      <c r="I98" s="10" t="inlineStr"/>
+    </row>
+    <row r="99" ht="25" customHeight="1">
+      <c r="A99" s="9" t="inlineStr">
         <is>
           <t>7.1.2</t>
         </is>
       </c>
-      <c r="B99" s="11" t="inlineStr"/>
+      <c r="B99" s="10" t="inlineStr"/>
       <c r="C99" s="11" t="inlineStr"/>
-      <c r="D99" s="12" t="inlineStr">
+      <c r="D99" s="11" t="inlineStr">
         <is>
           <t>청구서 조회</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr"/>
-      <c r="F99" s="11" t="inlineStr">
-        <is>
-          <t>청구내역 및 이력 조회</t>
-        </is>
-      </c>
-      <c r="G99" s="11" t="inlineStr">
+      <c r="F99" s="12" t="inlineStr">
+        <is>
+          <t>청구서 목록 및 항목별 상세 내역 조회. 조회 조건: 회원명·기간·운송수단·청구상태(UNPAID/PARTIAL/PAID).</t>
+        </is>
+      </c>
+      <c r="G99" s="10" t="inlineStr">
         <is>
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H99" s="20" t="inlineStr">
+      <c r="H99" s="21" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I99" s="11" t="inlineStr"/>
-    </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="10" t="inlineStr">
+      <c r="I99" s="10" t="inlineStr"/>
+    </row>
+    <row r="100" ht="24" customHeight="1">
+      <c r="A100" s="9" t="inlineStr">
         <is>
           <t>7.1.3</t>
         </is>
       </c>
-      <c r="B100" s="11" t="inlineStr"/>
+      <c r="B100" s="10" t="inlineStr"/>
       <c r="C100" s="11" t="inlineStr"/>
-      <c r="D100" s="12" t="inlineStr">
+      <c r="D100" s="11" t="inlineStr">
         <is>
           <t>청구서 출력</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr"/>
-      <c r="F100" s="11" t="inlineStr">
-        <is>
-          <t>청구서 PDF 출력</t>
-        </is>
-      </c>
-      <c r="G100" s="11" t="inlineStr">
+      <c r="F100" s="12" t="inlineStr">
+        <is>
+          <t>청구서를 PDF로 생성하여 출력 또는 다운로드. 청구서 내 항목별 운송비·Extra Charge·합계금액 포함.</t>
+        </is>
+      </c>
+      <c r="G100" s="10" t="inlineStr">
         <is>
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H100" s="20" t="inlineStr">
+      <c r="H100" s="21" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I100" s="11" t="inlineStr"/>
-    </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="A101" s="7" t="inlineStr">
+      <c r="I100" s="10" t="inlineStr"/>
+    </row>
+    <row r="101" ht="17" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr"/>
-      <c r="C101" s="9" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr"/>
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>입금 관리</t>
         </is>
       </c>
-      <c r="D101" s="8" t="inlineStr"/>
-      <c r="E101" s="8" t="inlineStr"/>
-      <c r="F101" s="8" t="inlineStr"/>
-      <c r="G101" s="8" t="inlineStr"/>
-      <c r="H101" s="19" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr"/>
+      <c r="E101" s="7" t="inlineStr"/>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>청구서별 입금 처리 및 미수금을 관리.</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr"/>
+      <c r="H101" s="20" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I101" s="8" t="inlineStr"/>
-    </row>
-    <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="10" t="inlineStr">
+      <c r="I101" s="7" t="inlineStr"/>
+    </row>
+    <row r="102" ht="24" customHeight="1">
+      <c r="A102" s="9" t="inlineStr">
         <is>
           <t>7.2.1</t>
         </is>
       </c>
-      <c r="B102" s="11" t="inlineStr"/>
+      <c r="B102" s="10" t="inlineStr"/>
       <c r="C102" s="11" t="inlineStr"/>
-      <c r="D102" s="12" t="inlineStr">
+      <c r="D102" s="11" t="inlineStr">
         <is>
           <t>청구정보 생성</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr"/>
-      <c r="F102" s="11" t="inlineStr">
-        <is>
-          <t>회원별·기간별·운송수단별 청구정보 생성</t>
-        </is>
-      </c>
-      <c r="G102" s="11" t="inlineStr">
+      <c r="F102" s="12" t="inlineStr">
+        <is>
+          <t>회원별·기간별·운송수단별 청구정보를 생성하여 입금 요청 기반 데이터 마련. 청구 생성 시 대상 오더의 운송비 합산.</t>
+        </is>
+      </c>
+      <c r="G102" s="10" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H102" s="20" t="inlineStr">
+      <c r="H102" s="21" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I102" s="11" t="inlineStr"/>
-    </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="10" t="inlineStr">
+      <c r="I102" s="10" t="inlineStr"/>
+    </row>
+    <row r="103" ht="26" customHeight="1">
+      <c r="A103" s="9" t="inlineStr">
         <is>
           <t>7.2.2</t>
         </is>
       </c>
-      <c r="B103" s="11" t="inlineStr"/>
+      <c r="B103" s="10" t="inlineStr"/>
       <c r="C103" s="11" t="inlineStr"/>
-      <c r="D103" s="12" t="inlineStr">
+      <c r="D103" s="11" t="inlineStr">
         <is>
           <t>입금 확인</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr"/>
-      <c r="F103" s="11" t="inlineStr">
-        <is>
-          <t>청구서별 입금 여부 확인 및 처리</t>
-        </is>
-      </c>
-      <c r="G103" s="11" t="inlineStr">
+      <c r="F103" s="12" t="inlineStr">
+        <is>
+          <t>청구서별 입금 여부를 확인하고 입금액·입금일시·입금방법을 등록. 부분 입금 시 청구상태를 PARTIAL로, 전액 입금 시 PAID로 변경.</t>
+        </is>
+      </c>
+      <c r="G103" s="10" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H103" s="20" t="inlineStr">
+      <c r="H103" s="21" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I103" s="11" t="inlineStr"/>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="7" t="inlineStr">
+      <c r="I103" s="10" t="inlineStr"/>
+    </row>
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr"/>
-      <c r="C104" s="9" t="inlineStr">
+      <c r="B104" s="7" t="inlineStr"/>
+      <c r="C104" s="7" t="inlineStr">
         <is>
           <t>수입 관리</t>
         </is>
       </c>
-      <c r="D104" s="8" t="inlineStr"/>
-      <c r="E104" s="8" t="inlineStr"/>
+      <c r="D104" s="7" t="inlineStr"/>
+      <c r="E104" s="7" t="inlineStr"/>
       <c r="F104" s="8" t="inlineStr">
         <is>
-          <t>회원별/기간별/운송수단별 수입 현황 조회</t>
-        </is>
-      </c>
-      <c r="G104" s="8" t="inlineStr">
+          <t>회원별·기간별·운송수단별 수입 현황 조회. 운송비 합계·입금액·미수금을 집계하여 수익성 분석.</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H104" s="19" t="inlineStr">
+      <c r="H104" s="20" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I104" s="8" t="inlineStr"/>
-    </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="7" t="inlineStr">
+      <c r="I104" s="7" t="inlineStr"/>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>7.4</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr"/>
-      <c r="C105" s="9" t="inlineStr">
+      <c r="B105" s="7" t="inlineStr"/>
+      <c r="C105" s="7" t="inlineStr">
         <is>
           <t>비용 관리</t>
         </is>
       </c>
-      <c r="D105" s="8" t="inlineStr"/>
-      <c r="E105" s="8" t="inlineStr"/>
-      <c r="F105" s="8" t="inlineStr"/>
-      <c r="G105" s="8" t="inlineStr"/>
-      <c r="H105" s="19" t="inlineStr">
+      <c r="D105" s="7" t="inlineStr"/>
+      <c r="E105" s="7" t="inlineStr"/>
+      <c r="F105" s="8" t="inlineStr">
+        <is>
+          <t>운송사별 실제 운송원가 조회. 수입 대비 원가를 비교하여 수익 분석.</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr"/>
+      <c r="H105" s="20" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I105" s="8" t="inlineStr"/>
-    </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="10" t="inlineStr">
+      <c r="I105" s="7" t="inlineStr"/>
+    </row>
+    <row r="106" ht="21" customHeight="1">
+      <c r="A106" s="9" t="inlineStr">
         <is>
           <t>7.4.1</t>
         </is>
       </c>
-      <c r="B106" s="11" t="inlineStr"/>
+      <c r="B106" s="10" t="inlineStr"/>
       <c r="C106" s="11" t="inlineStr"/>
-      <c r="D106" s="12" t="inlineStr">
+      <c r="D106" s="11" t="inlineStr">
         <is>
           <t>항운(AIR) 비용 조회</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr"/>
-      <c r="F106" s="11" t="inlineStr">
-        <is>
-          <t>항운사별·기간별 원가 조회</t>
-        </is>
-      </c>
-      <c r="G106" s="11" t="inlineStr">
+      <c r="F106" s="12" t="inlineStr">
+        <is>
+          <t>항공사별·기간별 항운 원가(실제 지불 비용) 조회. 운송원가 마스터 기준으로 집계.</t>
+        </is>
+      </c>
+      <c r="G106" s="10" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H106" s="20" t="inlineStr">
+      <c r="H106" s="21" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I106" s="11" t="inlineStr"/>
-    </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="10" t="inlineStr">
+      <c r="I106" s="10" t="inlineStr"/>
+    </row>
+    <row r="107" ht="16" customHeight="1">
+      <c r="A107" s="9" t="inlineStr">
         <is>
           <t>7.4.2</t>
         </is>
       </c>
-      <c r="B107" s="11" t="inlineStr"/>
+      <c r="B107" s="10" t="inlineStr"/>
       <c r="C107" s="11" t="inlineStr"/>
-      <c r="D107" s="12" t="inlineStr">
+      <c r="D107" s="11" t="inlineStr">
         <is>
           <t>해운(SEA) 비용 조회</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr"/>
-      <c r="F107" s="11" t="inlineStr">
-        <is>
-          <t>해운사별·기간별 원가 조회</t>
-        </is>
-      </c>
-      <c r="G107" s="11" t="inlineStr">
+      <c r="F107" s="12" t="inlineStr">
+        <is>
+          <t>선사별·기간별 해운 원가 조회.</t>
+        </is>
+      </c>
+      <c r="G107" s="10" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H107" s="20" t="inlineStr">
+      <c r="H107" s="21" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I107" s="11" t="inlineStr"/>
-    </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="10" t="inlineStr">
+      <c r="I107" s="10" t="inlineStr"/>
+    </row>
+    <row r="108" ht="17" customHeight="1">
+      <c r="A108" s="9" t="inlineStr">
         <is>
           <t>7.4.3</t>
         </is>
       </c>
-      <c r="B108" s="11" t="inlineStr"/>
+      <c r="B108" s="10" t="inlineStr"/>
       <c r="C108" s="11" t="inlineStr"/>
-      <c r="D108" s="12" t="inlineStr">
+      <c r="D108" s="11" t="inlineStr">
         <is>
           <t>택배(CIR) 비용 조회</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr"/>
-      <c r="F108" s="11" t="inlineStr">
-        <is>
-          <t>택배사별·기간별 원가 조회</t>
-        </is>
-      </c>
-      <c r="G108" s="11" t="inlineStr">
+      <c r="F108" s="12" t="inlineStr">
+        <is>
+          <t>택배사별·기간별 택배 원가 조회.</t>
+        </is>
+      </c>
+      <c r="G108" s="10" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H108" s="20" t="inlineStr">
+      <c r="H108" s="21" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I108" s="11" t="inlineStr"/>
-    </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="7" t="inlineStr">
+      <c r="I108" s="10" t="inlineStr"/>
+    </row>
+    <row r="109" ht="17" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr"/>
-      <c r="C109" s="9" t="inlineStr">
+      <c r="B109" s="7" t="inlineStr"/>
+      <c r="C109" s="7" t="inlineStr">
         <is>
           <t>세금계산서</t>
         </is>
       </c>
-      <c r="D109" s="8" t="inlineStr"/>
-      <c r="E109" s="8" t="inlineStr"/>
-      <c r="F109" s="8" t="inlineStr"/>
-      <c r="G109" s="8" t="inlineStr"/>
-      <c r="H109" s="19" t="inlineStr">
+      <c r="D109" s="7" t="inlineStr"/>
+      <c r="E109" s="7" t="inlineStr"/>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>청구서 기준 세금계산서 발행 및 조회.</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr"/>
+      <c r="H109" s="20" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I109" s="8" t="inlineStr"/>
-    </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="10" t="inlineStr">
+      <c r="I109" s="7" t="inlineStr"/>
+    </row>
+    <row r="110" ht="21" customHeight="1">
+      <c r="A110" s="9" t="inlineStr">
         <is>
           <t>7.5.1</t>
         </is>
       </c>
-      <c r="B110" s="11" t="inlineStr"/>
+      <c r="B110" s="10" t="inlineStr"/>
       <c r="C110" s="11" t="inlineStr"/>
-      <c r="D110" s="12" t="inlineStr">
+      <c r="D110" s="11" t="inlineStr">
         <is>
           <t>세금계산서 조회</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr"/>
-      <c r="F110" s="11" t="inlineStr">
-        <is>
-          <t>세금계산서 목록 조회</t>
-        </is>
-      </c>
-      <c r="G110" s="11" t="inlineStr">
+      <c r="F110" s="12" t="inlineStr">
+        <is>
+          <t>발행된 세금계산서 목록 조회. 세금계산서번호·발행일·공급가액·세액·합계금액 확인.</t>
+        </is>
+      </c>
+      <c r="G110" s="10" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H110" s="20" t="inlineStr">
+      <c r="H110" s="21" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I110" s="11" t="inlineStr"/>
+      <c r="I110" s="10" t="inlineStr"/>
     </row>
     <row r="111" ht="18" customHeight="1">
-      <c r="A111" s="10" t="inlineStr">
+      <c r="A111" s="9" t="inlineStr">
         <is>
           <t>7.5.2</t>
         </is>
       </c>
-      <c r="B111" s="11" t="inlineStr"/>
+      <c r="B111" s="10" t="inlineStr"/>
       <c r="C111" s="11" t="inlineStr"/>
-      <c r="D111" s="12" t="inlineStr">
+      <c r="D111" s="11" t="inlineStr">
         <is>
           <t>세금계산서 출력</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr"/>
-      <c r="F111" s="11" t="inlineStr">
-        <is>
-          <t>세금계산서 PDF 출력</t>
-        </is>
-      </c>
-      <c r="G111" s="11" t="inlineStr">
+      <c r="F111" s="12" t="inlineStr">
+        <is>
+          <t>세금계산서를 PDF로 생성하여 출력 또는 다운로드.</t>
+        </is>
+      </c>
+      <c r="G111" s="10" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H111" s="20" t="inlineStr">
+      <c r="H111" s="21" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I111" s="11" t="inlineStr"/>
-    </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="7" t="inlineStr">
+      <c r="I111" s="10" t="inlineStr"/>
+    </row>
+    <row r="112" ht="24" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
         <is>
           <t>7.6</t>
         </is>
       </c>
-      <c r="B112" s="8" t="inlineStr"/>
-      <c r="C112" s="9" t="inlineStr">
+      <c r="B112" s="7" t="inlineStr"/>
+      <c r="C112" s="7" t="inlineStr">
         <is>
           <t>운송원가 관리</t>
         </is>
       </c>
-      <c r="D112" s="8" t="inlineStr"/>
-      <c r="E112" s="8" t="inlineStr"/>
-      <c r="F112" s="8" t="inlineStr"/>
-      <c r="G112" s="8" t="inlineStr"/>
-      <c r="H112" s="19" t="inlineStr">
+      <c r="D112" s="7" t="inlineStr"/>
+      <c r="E112" s="7" t="inlineStr"/>
+      <c r="F112" s="8" t="inlineStr">
+        <is>
+          <t>서비스·운송사·구간별 운송원가 기준 데이터를 등록·관리. 원가 데이터는 운송비 자동 계산의 기초 자료로 사용됨.</t>
+        </is>
+      </c>
+      <c r="G112" s="7" t="inlineStr"/>
+      <c r="H112" s="20" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I112" s="8" t="inlineStr"/>
-    </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="10" t="inlineStr">
+      <c r="I112" s="7" t="inlineStr"/>
+    </row>
+    <row r="113" ht="26" customHeight="1">
+      <c r="A113" s="9" t="inlineStr">
         <is>
           <t>7.6.1</t>
         </is>
       </c>
-      <c r="B113" s="11" t="inlineStr"/>
+      <c r="B113" s="10" t="inlineStr"/>
       <c r="C113" s="11" t="inlineStr"/>
-      <c r="D113" s="12" t="inlineStr">
+      <c r="D113" s="11" t="inlineStr">
         <is>
           <t>운송원가 등록</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr"/>
-      <c r="F113" s="11" t="inlineStr">
-        <is>
-          <t>서비스·운송사·구간별 원가 등록</t>
-        </is>
-      </c>
-      <c r="G113" s="11" t="inlineStr">
+      <c r="F113" s="12" t="inlineStr">
+        <is>
+          <t>서비스구분(AIR/SEA/CIR)·운송사·출발지·도착지·중량구간별 단위원가 등록. 적용 시작일·종료일을 설정하여 기간별 원가 관리.</t>
+        </is>
+      </c>
+      <c r="G113" s="10" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="H113" s="20" t="inlineStr">
+      <c r="H113" s="21" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I113" s="11" t="inlineStr"/>
-    </row>
-    <row r="114" ht="18" customHeight="1">
-      <c r="A114" s="10" t="inlineStr">
+      <c r="I113" s="10" t="inlineStr"/>
+    </row>
+    <row r="114" ht="22" customHeight="1">
+      <c r="A114" s="9" t="inlineStr">
         <is>
           <t>7.6.2</t>
         </is>
       </c>
-      <c r="B114" s="11" t="inlineStr"/>
+      <c r="B114" s="10" t="inlineStr"/>
       <c r="C114" s="11" t="inlineStr"/>
-      <c r="D114" s="12" t="inlineStr">
+      <c r="D114" s="11" t="inlineStr">
         <is>
           <t>운송원가 수정</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr"/>
-      <c r="F114" s="11" t="inlineStr">
-        <is>
-          <t>기등록 원가 수정</t>
-        </is>
-      </c>
-      <c r="G114" s="11" t="inlineStr">
+      <c r="F114" s="12" t="inlineStr">
+        <is>
+          <t>기등록된 운송원가 수정. 수정 시 기존 원가의 적용종료일을 자동 설정하고 새 원가를 등록.</t>
+        </is>
+      </c>
+      <c r="G114" s="10" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="H114" s="20" t="inlineStr">
+      <c r="H114" s="21" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I114" s="11" t="inlineStr"/>
-    </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="3" t="inlineStr">
+      <c r="I114" s="10" t="inlineStr"/>
+    </row>
+    <row r="115" ht="21" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B115" s="4" t="inlineStr">
+      <c r="B115" s="3" t="inlineStr">
         <is>
           <t>VOC 관리</t>
         </is>
       </c>
-      <c r="C115" s="5" t="inlineStr"/>
-      <c r="D115" s="5" t="inlineStr"/>
-      <c r="E115" s="5" t="inlineStr"/>
-      <c r="F115" s="5" t="inlineStr"/>
-      <c r="G115" s="5" t="inlineStr"/>
-      <c r="H115" s="19" t="inlineStr">
+      <c r="C115" s="3" t="inlineStr"/>
+      <c r="D115" s="3" t="inlineStr"/>
+      <c r="E115" s="3" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>오더별 고객 불만·문의(Voice of Customer)를 접수·처리하는 기능.</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr"/>
+      <c r="H115" s="20" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I115" s="5" t="inlineStr"/>
-    </row>
-    <row r="116" ht="18" customHeight="1">
-      <c r="A116" s="7" t="inlineStr">
+      <c r="I115" s="3" t="inlineStr"/>
+    </row>
+    <row r="116" ht="23" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="B116" s="8" t="inlineStr"/>
-      <c r="C116" s="9" t="inlineStr">
+      <c r="B116" s="7" t="inlineStr"/>
+      <c r="C116" s="7" t="inlineStr">
         <is>
           <t>VOC 등록</t>
         </is>
       </c>
-      <c r="D116" s="8" t="inlineStr"/>
-      <c r="E116" s="8" t="inlineStr"/>
+      <c r="D116" s="7" t="inlineStr"/>
+      <c r="E116" s="7" t="inlineStr"/>
       <c r="F116" s="8" t="inlineStr">
         <is>
-          <t>오더별 고객 불만/문의 등록</t>
-        </is>
-      </c>
-      <c r="G116" s="8" t="inlineStr">
+          <t>오더를 선택하여 불만·문의 내용을 등록. 등록 후 초기 처리상태는 OPEN. 담당자에게 알림 발송.</t>
+        </is>
+      </c>
+      <c r="G116" s="7" t="inlineStr">
         <is>
           <t>회원</t>
         </is>
       </c>
-      <c r="H116" s="19" t="inlineStr">
+      <c r="H116" s="20" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I116" s="8" t="inlineStr"/>
-    </row>
-    <row r="117" ht="18" customHeight="1">
-      <c r="A117" s="7" t="inlineStr">
+      <c r="I116" s="7" t="inlineStr"/>
+    </row>
+    <row r="117" ht="27" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="B117" s="8" t="inlineStr"/>
-      <c r="C117" s="9" t="inlineStr">
+      <c r="B117" s="7" t="inlineStr"/>
+      <c r="C117" s="7" t="inlineStr">
         <is>
           <t>VOC 답변</t>
         </is>
       </c>
-      <c r="D117" s="8" t="inlineStr"/>
-      <c r="E117" s="8" t="inlineStr"/>
+      <c r="D117" s="7" t="inlineStr"/>
+      <c r="E117" s="7" t="inlineStr"/>
       <c r="F117" s="8" t="inlineStr">
         <is>
-          <t>담당자 답변 처리</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr">
+          <t>접수된 VOC에 담당자가 답변 등록. 답변 완료 시 처리상태를 IN_PROGRESS 또는 CLOSED로 변경. 답변 등록 후 고객에게 알림 발송.</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H117" s="19" t="inlineStr">
+      <c r="H117" s="20" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I117" s="8" t="inlineStr"/>
-    </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="7" t="inlineStr">
+      <c r="I117" s="7" t="inlineStr"/>
+    </row>
+    <row r="118" ht="28" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="B118" s="8" t="inlineStr"/>
-      <c r="C118" s="9" t="inlineStr">
+      <c r="B118" s="7" t="inlineStr"/>
+      <c r="C118" s="7" t="inlineStr">
         <is>
           <t>VOC 조회</t>
         </is>
       </c>
-      <c r="D118" s="8" t="inlineStr"/>
-      <c r="E118" s="8" t="inlineStr"/>
+      <c r="D118" s="7" t="inlineStr"/>
+      <c r="E118" s="7" t="inlineStr"/>
       <c r="F118" s="8" t="inlineStr">
         <is>
-          <t>VOC 목록 및 상태 조회</t>
-        </is>
-      </c>
-      <c r="G118" s="8" t="inlineStr">
+          <t>VOC 목록 및 처리 상태 조회. 조회 조건: 오더번호·처리상태(OPEN/IN_PROGRESS/CLOSED)·등록일자. 회원은 본인 VOC만 조회 가능.</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
         <is>
           <t>회원/운영자/관리자</t>
         </is>
       </c>
-      <c r="H118" s="19" t="inlineStr">
+      <c r="H118" s="20" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="I118" s="8" t="inlineStr"/>
-    </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="3" t="inlineStr">
+      <c r="I118" s="7" t="inlineStr"/>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B119" s="4" t="inlineStr">
+      <c r="B119" s="3" t="inlineStr">
         <is>
           <t>시스템관리</t>
         </is>
       </c>
-      <c r="C119" s="5" t="inlineStr"/>
-      <c r="D119" s="5" t="inlineStr"/>
-      <c r="E119" s="5" t="inlineStr"/>
-      <c r="F119" s="5" t="inlineStr"/>
-      <c r="G119" s="5" t="inlineStr"/>
-      <c r="H119" s="21" t="inlineStr">
+      <c r="C119" s="3" t="inlineStr"/>
+      <c r="D119" s="3" t="inlineStr"/>
+      <c r="E119" s="3" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>시스템 운영에 필요한 메뉴·코드·권한·알림·통계·데이터 백업을 관리.</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr"/>
+      <c r="H119" s="22" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I119" s="5" t="inlineStr"/>
-    </row>
-    <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="7" t="inlineStr">
+      <c r="I119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
         <is>
           <t>9.1</t>
         </is>
       </c>
-      <c r="B120" s="8" t="inlineStr"/>
-      <c r="C120" s="9" t="inlineStr">
+      <c r="B120" s="7" t="inlineStr"/>
+      <c r="C120" s="7" t="inlineStr">
         <is>
           <t>메뉴 관리</t>
         </is>
       </c>
-      <c r="D120" s="8" t="inlineStr"/>
-      <c r="E120" s="8" t="inlineStr"/>
-      <c r="F120" s="8" t="inlineStr"/>
-      <c r="G120" s="8" t="inlineStr"/>
-      <c r="H120" s="21" t="inlineStr">
+      <c r="D120" s="7" t="inlineStr"/>
+      <c r="E120" s="7" t="inlineStr"/>
+      <c r="F120" s="8" t="inlineStr">
+        <is>
+          <t>시스템 화면 메뉴 구조를 등록·수정·삭제·조회. 계층형(트리) 구조 지원.</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr"/>
+      <c r="H120" s="22" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I120" s="8" t="inlineStr"/>
-    </row>
-    <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="10" t="inlineStr">
+      <c r="I120" s="7" t="inlineStr"/>
+    </row>
+    <row r="121" ht="22" customHeight="1">
+      <c r="A121" s="9" t="inlineStr">
         <is>
           <t>9.1.1</t>
         </is>
       </c>
-      <c r="B121" s="11" t="inlineStr"/>
+      <c r="B121" s="10" t="inlineStr"/>
       <c r="C121" s="11" t="inlineStr"/>
-      <c r="D121" s="12" t="inlineStr">
+      <c r="D121" s="11" t="inlineStr">
         <is>
           <t>메뉴 등록</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr"/>
-      <c r="F121" s="11" t="inlineStr">
-        <is>
-          <t>메뉴 신규 등록</t>
-        </is>
-      </c>
-      <c r="G121" s="11" t="inlineStr">
+      <c r="F121" s="12" t="inlineStr">
+        <is>
+          <t>새 메뉴 항목 등록. 상위메뉴·메뉴명·URL·정렬순서 입력. 최상위 메뉴는 상위메뉴 없이 등록.</t>
+        </is>
+      </c>
+      <c r="G121" s="10" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="H121" s="22" t="inlineStr">
+      <c r="H121" s="23" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I121" s="11" t="inlineStr"/>
-    </row>
-    <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="10" t="inlineStr">
+      <c r="I121" s="10" t="inlineStr"/>
+    </row>
+    <row r="122" ht="17" customHeight="1">
+      <c r="A122" s="9" t="inlineStr">
         <is>
           <t>9.1.2</t>
         </is>
       </c>
-      <c r="B122" s="11" t="inlineStr"/>
+      <c r="B122" s="10" t="inlineStr"/>
       <c r="C122" s="11" t="inlineStr"/>
-      <c r="D122" s="12" t="inlineStr">
+      <c r="D122" s="11" t="inlineStr">
         <is>
           <t>메뉴 수정</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr"/>
-      <c r="F122" s="11" t="inlineStr">
-        <is>
-          <t>메뉴명·URL·순서 수정</t>
-        </is>
-      </c>
-      <c r="G122" s="11" t="inlineStr">
+      <c r="F122" s="12" t="inlineStr">
+        <is>
+          <t>메뉴명·URL·정렬순서·사용여부 수정.</t>
+        </is>
+      </c>
+      <c r="G122" s="10" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="H122" s="22" t="inlineStr">
+      <c r="H122" s="23" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I122" s="11" t="inlineStr"/>
-    </row>
-    <row r="123" ht="18" customHeight="1">
-      <c r="A123" s="10" t="inlineStr">
+      <c r="I122" s="10" t="inlineStr"/>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="9" t="inlineStr">
         <is>
           <t>9.1.3</t>
         </is>
       </c>
-      <c r="B123" s="11" t="inlineStr"/>
+      <c r="B123" s="10" t="inlineStr"/>
       <c r="C123" s="11" t="inlineStr"/>
-      <c r="D123" s="12" t="inlineStr">
+      <c r="D123" s="11" t="inlineStr">
         <is>
           <t>메뉴 삭제</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr"/>
-      <c r="F123" s="11" t="inlineStr">
-        <is>
-          <t>메뉴 삭제 (사용여부 N 처리)</t>
-        </is>
-      </c>
-      <c r="G123" s="11" t="inlineStr">
+      <c r="F123" s="12" t="inlineStr">
+        <is>
+          <t>메뉴 삭제(사용여부 N 처리). 하위 메뉴가 있는 경우 삭제 불가.</t>
+        </is>
+      </c>
+      <c r="G123" s="10" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="H123" s="22" t="inlineStr">
+      <c r="H123" s="23" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I123" s="11" t="inlineStr"/>
-    </row>
-    <row r="124" ht="18" customHeight="1">
-      <c r="A124" s="10" t="inlineStr">
+      <c r="I123" s="10" t="inlineStr"/>
+    </row>
+    <row r="124" ht="19" customHeight="1">
+      <c r="A124" s="9" t="inlineStr">
         <is>
           <t>9.1.4</t>
         </is>
       </c>
-      <c r="B124" s="11" t="inlineStr"/>
+      <c r="B124" s="10" t="inlineStr"/>
       <c r="C124" s="11" t="inlineStr"/>
-      <c r="D124" s="12" t="inlineStr">
+      <c r="D124" s="11" t="inlineStr">
         <is>
           <t>메뉴 조회</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr"/>
-      <c r="F124" s="11" t="inlineStr">
-        <is>
-          <t>메뉴 목록 조회</t>
-        </is>
-      </c>
-      <c r="G124" s="11" t="inlineStr">
+      <c r="F124" s="12" t="inlineStr">
+        <is>
+          <t>전체 메뉴 트리 구조 조회. 권한별 접근 가능 메뉴 필터링.</t>
+        </is>
+      </c>
+      <c r="G124" s="10" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="H124" s="22" t="inlineStr">
+      <c r="H124" s="23" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I124" s="11" t="inlineStr"/>
-    </row>
-    <row r="125" ht="18" customHeight="1">
-      <c r="A125" s="7" t="inlineStr">
+      <c r="I124" s="10" t="inlineStr"/>
+    </row>
+    <row r="125" ht="19" customHeight="1">
+      <c r="A125" s="6" t="inlineStr">
         <is>
           <t>9.2</t>
         </is>
       </c>
-      <c r="B125" s="8" t="inlineStr"/>
-      <c r="C125" s="9" t="inlineStr">
+      <c r="B125" s="7" t="inlineStr"/>
+      <c r="C125" s="7" t="inlineStr">
         <is>
           <t>코드 관리</t>
         </is>
       </c>
-      <c r="D125" s="8" t="inlineStr"/>
-      <c r="E125" s="8" t="inlineStr"/>
-      <c r="F125" s="8" t="inlineStr"/>
-      <c r="G125" s="8" t="inlineStr"/>
-      <c r="H125" s="21" t="inlineStr">
+      <c r="D125" s="7" t="inlineStr"/>
+      <c r="E125" s="7" t="inlineStr"/>
+      <c r="F125" s="8" t="inlineStr">
+        <is>
+          <t>시스템 공통 코드(상태값·분류값 등)를 그룹별로 등록·관리.</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr"/>
+      <c r="H125" s="22" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I125" s="8" t="inlineStr"/>
-    </row>
-    <row r="126" ht="18" customHeight="1">
-      <c r="A126" s="10" t="inlineStr">
+      <c r="I125" s="7" t="inlineStr"/>
+    </row>
+    <row r="126" ht="19" customHeight="1">
+      <c r="A126" s="9" t="inlineStr">
         <is>
           <t>9.2.1</t>
         </is>
       </c>
-      <c r="B126" s="11" t="inlineStr"/>
+      <c r="B126" s="10" t="inlineStr"/>
       <c r="C126" s="11" t="inlineStr"/>
-      <c r="D126" s="12" t="inlineStr">
+      <c r="D126" s="11" t="inlineStr">
         <is>
           <t>코드 등록</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr"/>
-      <c r="F126" s="11" t="inlineStr">
-        <is>
-          <t>공통 코드 신규 등록</t>
-        </is>
-      </c>
-      <c r="G126" s="11" t="inlineStr">
+      <c r="F126" s="12" t="inlineStr">
+        <is>
+          <t>코드그룹 내 새 코드를 등록. 코드값·코드명·정렬순서 입력.</t>
+        </is>
+      </c>
+      <c r="G126" s="10" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="H126" s="22" t="inlineStr">
+      <c r="H126" s="23" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I126" s="11" t="inlineStr"/>
-    </row>
-    <row r="127" ht="18" customHeight="1">
-      <c r="A127" s="10" t="inlineStr">
+      <c r="I126" s="10" t="inlineStr"/>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="9" t="inlineStr">
         <is>
           <t>9.2.2</t>
         </is>
       </c>
-      <c r="B127" s="11" t="inlineStr"/>
+      <c r="B127" s="10" t="inlineStr"/>
       <c r="C127" s="11" t="inlineStr"/>
-      <c r="D127" s="12" t="inlineStr">
+      <c r="D127" s="11" t="inlineStr">
         <is>
           <t>코드 수정</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr"/>
-      <c r="F127" s="11" t="inlineStr">
-        <is>
-          <t>코드명·정렬순서 수정</t>
-        </is>
-      </c>
-      <c r="G127" s="11" t="inlineStr">
+      <c r="F127" s="12" t="inlineStr">
+        <is>
+          <t>코드명·정렬순서 수정. 코드값 변경은 시스템 영향 확인 후 처리.</t>
+        </is>
+      </c>
+      <c r="G127" s="10" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="H127" s="22" t="inlineStr">
+      <c r="H127" s="23" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I127" s="11" t="inlineStr"/>
-    </row>
-    <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="10" t="inlineStr">
+      <c r="I127" s="10" t="inlineStr"/>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="9" t="inlineStr">
         <is>
           <t>9.2.3</t>
         </is>
       </c>
-      <c r="B128" s="11" t="inlineStr"/>
+      <c r="B128" s="10" t="inlineStr"/>
       <c r="C128" s="11" t="inlineStr"/>
-      <c r="D128" s="12" t="inlineStr">
+      <c r="D128" s="11" t="inlineStr">
         <is>
           <t>코드 삭제</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr"/>
-      <c r="F128" s="11" t="inlineStr">
-        <is>
-          <t>코드 삭제 (사용여부 N 처리)</t>
-        </is>
-      </c>
-      <c r="G128" s="11" t="inlineStr">
+      <c r="F128" s="12" t="inlineStr">
+        <is>
+          <t>코드 삭제(사용여부 N 처리). 실제로 사용 중인 코드는 삭제 불가.</t>
+        </is>
+      </c>
+      <c r="G128" s="10" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="H128" s="22" t="inlineStr">
+      <c r="H128" s="23" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I128" s="11" t="inlineStr"/>
-    </row>
-    <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="10" t="inlineStr">
+      <c r="I128" s="10" t="inlineStr"/>
+    </row>
+    <row r="129" ht="17" customHeight="1">
+      <c r="A129" s="9" t="inlineStr">
         <is>
           <t>9.2.4</t>
         </is>
       </c>
-      <c r="B129" s="11" t="inlineStr"/>
+      <c r="B129" s="10" t="inlineStr"/>
       <c r="C129" s="11" t="inlineStr"/>
-      <c r="D129" s="12" t="inlineStr">
+      <c r="D129" s="11" t="inlineStr">
         <is>
           <t>코드 조회</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr"/>
-      <c r="F129" s="11" t="inlineStr">
-        <is>
-          <t>코드 목록 조회</t>
-        </is>
-      </c>
-      <c r="G129" s="11" t="inlineStr">
+      <c r="F129" s="12" t="inlineStr">
+        <is>
+          <t>코드그룹별 전체 코드 목록 조회.</t>
+        </is>
+      </c>
+      <c r="G129" s="10" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="H129" s="22" t="inlineStr">
+      <c r="H129" s="23" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I129" s="11" t="inlineStr"/>
-    </row>
-    <row r="130" ht="18" customHeight="1">
-      <c r="A130" s="7" t="inlineStr">
+      <c r="I129" s="10" t="inlineStr"/>
+    </row>
+    <row r="130" ht="28" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
         <is>
           <t>9.3</t>
         </is>
       </c>
-      <c r="B130" s="8" t="inlineStr"/>
-      <c r="C130" s="9" t="inlineStr">
+      <c r="B130" s="7" t="inlineStr"/>
+      <c r="C130" s="7" t="inlineStr">
         <is>
           <t>권한 관리</t>
         </is>
       </c>
-      <c r="D130" s="8" t="inlineStr"/>
-      <c r="E130" s="8" t="inlineStr"/>
+      <c r="D130" s="7" t="inlineStr"/>
+      <c r="E130" s="7" t="inlineStr"/>
       <c r="F130" s="8" t="inlineStr">
         <is>
-          <t>역할(Role)별 메뉴 접근 권한 설정</t>
-        </is>
-      </c>
-      <c r="G130" s="8" t="inlineStr">
+          <t>역할(Role)을 정의하고 메뉴별 접근 권한을 설정. 역할 예: ADMIN·OPERATOR·INDIVIDUAL·CORPORATE·DEPT_MANAGER.</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="H130" s="21" t="inlineStr">
+      <c r="H130" s="22" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I130" s="8" t="inlineStr"/>
-    </row>
-    <row r="131" ht="18" customHeight="1">
-      <c r="A131" s="7" t="inlineStr">
+      <c r="I130" s="7" t="inlineStr"/>
+    </row>
+    <row r="131" ht="25" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
       </c>
-      <c r="B131" s="8" t="inlineStr"/>
-      <c r="C131" s="9" t="inlineStr">
+      <c r="B131" s="7" t="inlineStr"/>
+      <c r="C131" s="7" t="inlineStr">
         <is>
           <t>택배사 관리</t>
         </is>
       </c>
-      <c r="D131" s="8" t="inlineStr"/>
-      <c r="E131" s="8" t="inlineStr"/>
+      <c r="D131" s="7" t="inlineStr"/>
+      <c r="E131" s="7" t="inlineStr"/>
       <c r="F131" s="8" t="inlineStr">
         <is>
-          <t>택배사 정보 등록/수정/삭제/조회</t>
-        </is>
-      </c>
-      <c r="G131" s="8" t="inlineStr">
+          <t>서비스에서 사용할 택배사 정보를 등록·수정·삭제·조회. 택배사코드·택배사명(한글/영문)·서비스국가·Tracking URL 관리.</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="H131" s="6" t="inlineStr">
+      <c r="H131" s="5" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="I131" s="8" t="inlineStr"/>
-    </row>
-    <row r="132" ht="18" customHeight="1">
-      <c r="A132" s="7" t="inlineStr">
+      <c r="I131" s="7" t="inlineStr">
+        <is>
+          <t>기초코드로 Phase 1 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="19" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
       </c>
-      <c r="B132" s="8" t="inlineStr"/>
-      <c r="C132" s="9" t="inlineStr">
+      <c r="B132" s="7" t="inlineStr"/>
+      <c r="C132" s="7" t="inlineStr">
         <is>
           <t>알림 관리</t>
         </is>
       </c>
-      <c r="D132" s="8" t="inlineStr"/>
-      <c r="E132" s="8" t="inlineStr"/>
-      <c r="F132" s="8" t="inlineStr"/>
-      <c r="G132" s="8" t="inlineStr"/>
-      <c r="H132" s="21" t="inlineStr">
+      <c r="D132" s="7" t="inlineStr"/>
+      <c r="E132" s="7" t="inlineStr"/>
+      <c r="F132" s="8" t="inlineStr">
+        <is>
+          <t>회원 대상 알림(공지·운송상태 변경 등)을 생성·발송·관리.</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr"/>
+      <c r="H132" s="22" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I132" s="8" t="inlineStr"/>
-    </row>
-    <row r="133" ht="18" customHeight="1">
-      <c r="A133" s="10" t="inlineStr">
+      <c r="I132" s="7" t="inlineStr"/>
+    </row>
+    <row r="133" ht="21" customHeight="1">
+      <c r="A133" s="9" t="inlineStr">
         <is>
           <t>9.5.1</t>
         </is>
       </c>
-      <c r="B133" s="11" t="inlineStr"/>
+      <c r="B133" s="10" t="inlineStr"/>
       <c r="C133" s="11" t="inlineStr"/>
-      <c r="D133" s="12" t="inlineStr">
+      <c r="D133" s="11" t="inlineStr">
         <is>
           <t>알림 등록</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr"/>
-      <c r="F133" s="11" t="inlineStr">
-        <is>
-          <t>알림 내용·대상 설정</t>
-        </is>
-      </c>
-      <c r="G133" s="11" t="inlineStr">
+      <c r="F133" s="12" t="inlineStr">
+        <is>
+          <t>알림 제목·내용·발송 대상(전체/개인/법인) 설정. 발송 예약 시각 설정 가능.</t>
+        </is>
+      </c>
+      <c r="G133" s="10" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="H133" s="22" t="inlineStr">
+      <c r="H133" s="23" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I133" s="11" t="inlineStr"/>
-    </row>
-    <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="10" t="inlineStr">
+      <c r="I133" s="10" t="inlineStr"/>
+    </row>
+    <row r="134" ht="19" customHeight="1">
+      <c r="A134" s="9" t="inlineStr">
         <is>
           <t>9.5.2</t>
         </is>
       </c>
-      <c r="B134" s="11" t="inlineStr"/>
+      <c r="B134" s="10" t="inlineStr"/>
       <c r="C134" s="11" t="inlineStr"/>
-      <c r="D134" s="12" t="inlineStr">
+      <c r="D134" s="11" t="inlineStr">
         <is>
           <t>알림 삭제</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr"/>
-      <c r="F134" s="11" t="inlineStr">
-        <is>
-          <t>등록된 알림 삭제</t>
-        </is>
-      </c>
-      <c r="G134" s="11" t="inlineStr">
+      <c r="F134" s="12" t="inlineStr">
+        <is>
+          <t>발송 전 미발송 알림 삭제. 발송 완료된 알림은 이력으로 보존.</t>
+        </is>
+      </c>
+      <c r="G134" s="10" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="H134" s="22" t="inlineStr">
+      <c r="H134" s="23" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I134" s="11" t="inlineStr"/>
-    </row>
-    <row r="135" ht="18" customHeight="1">
-      <c r="A135" s="10" t="inlineStr">
+      <c r="I134" s="10" t="inlineStr"/>
+    </row>
+    <row r="135" ht="26" customHeight="1">
+      <c r="A135" s="9" t="inlineStr">
         <is>
           <t>9.5.3</t>
         </is>
       </c>
-      <c r="B135" s="11" t="inlineStr"/>
+      <c r="B135" s="10" t="inlineStr"/>
       <c r="C135" s="11" t="inlineStr"/>
-      <c r="D135" s="12" t="inlineStr">
+      <c r="D135" s="11" t="inlineStr">
         <is>
           <t>알림 발송</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr"/>
-      <c r="F135" s="11" t="inlineStr">
-        <is>
-          <t>대상 회원에게 알림 전송</t>
-        </is>
-      </c>
-      <c r="G135" s="11" t="inlineStr">
+      <c r="F135" s="12" t="inlineStr">
+        <is>
+          <t>등록된 알림을 대상 회원에게 즉시 또는 예약 발송. 발송 채널: 앱 푸시·이메일(추후 확정). 발송 결과(SENT/FAILED) 기록.</t>
+        </is>
+      </c>
+      <c r="G135" s="10" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="H135" s="22" t="inlineStr">
+      <c r="H135" s="23" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I135" s="11" t="inlineStr"/>
-    </row>
-    <row r="136" ht="18" customHeight="1">
-      <c r="A136" s="10" t="inlineStr">
+      <c r="I135" s="10" t="inlineStr">
+        <is>
+          <t>발송채널 추후 확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="19" customHeight="1">
+      <c r="A136" s="9" t="inlineStr">
         <is>
           <t>9.5.4</t>
         </is>
       </c>
-      <c r="B136" s="11" t="inlineStr"/>
+      <c r="B136" s="10" t="inlineStr"/>
       <c r="C136" s="11" t="inlineStr"/>
-      <c r="D136" s="12" t="inlineStr">
+      <c r="D136" s="11" t="inlineStr">
         <is>
           <t>알림 조회</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr"/>
-      <c r="F136" s="11" t="inlineStr">
-        <is>
-          <t>발송 이력 조회</t>
-        </is>
-      </c>
-      <c r="G136" s="11" t="inlineStr">
+      <c r="F136" s="12" t="inlineStr">
+        <is>
+          <t>알림 발송 이력 조회. 발송상태·발송일시·대상 정보 확인.</t>
+        </is>
+      </c>
+      <c r="G136" s="10" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="H136" s="22" t="inlineStr">
+      <c r="H136" s="23" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I136" s="11" t="inlineStr"/>
-    </row>
-    <row r="137" ht="18" customHeight="1">
-      <c r="A137" s="7" t="inlineStr">
+      <c r="I136" s="10" t="inlineStr"/>
+    </row>
+    <row r="137" ht="19" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
         <is>
           <t>9.6</t>
         </is>
       </c>
-      <c r="B137" s="8" t="inlineStr"/>
-      <c r="C137" s="9" t="inlineStr">
+      <c r="B137" s="7" t="inlineStr"/>
+      <c r="C137" s="7" t="inlineStr">
         <is>
           <t>통계 관리</t>
         </is>
       </c>
-      <c r="D137" s="8" t="inlineStr"/>
-      <c r="E137" s="8" t="inlineStr"/>
-      <c r="F137" s="8" t="inlineStr"/>
-      <c r="G137" s="8" t="inlineStr"/>
-      <c r="H137" s="21" t="inlineStr">
+      <c r="D137" s="7" t="inlineStr"/>
+      <c r="E137" s="7" t="inlineStr"/>
+      <c r="F137" s="8" t="inlineStr">
+        <is>
+          <t>운송·비용 데이터를 집계하여 경영 현황을 파악하는 통계 기능.</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="inlineStr"/>
+      <c r="H137" s="22" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I137" s="8" t="inlineStr"/>
-    </row>
-    <row r="138" ht="18" customHeight="1">
-      <c r="A138" s="10" t="inlineStr">
+      <c r="I137" s="7" t="inlineStr"/>
+    </row>
+    <row r="138" ht="21" customHeight="1">
+      <c r="A138" s="9" t="inlineStr">
         <is>
           <t>9.6.1</t>
         </is>
       </c>
-      <c r="B138" s="11" t="inlineStr"/>
+      <c r="B138" s="10" t="inlineStr"/>
       <c r="C138" s="11" t="inlineStr"/>
-      <c r="D138" s="12" t="inlineStr">
+      <c r="D138" s="11" t="inlineStr">
         <is>
           <t>운송 통계</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr"/>
-      <c r="F138" s="11" t="inlineStr">
-        <is>
-          <t>운송수단별·기간별 통계</t>
-        </is>
-      </c>
-      <c r="G138" s="11" t="inlineStr">
+      <c r="F138" s="12" t="inlineStr">
+        <is>
+          <t>기간별·운송수단별·회원별 오더 건수·중량·CBM을 집계하여 운송 현황 통계 제공.</t>
+        </is>
+      </c>
+      <c r="G138" s="10" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H138" s="22" t="inlineStr">
+      <c r="H138" s="23" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I138" s="11" t="inlineStr"/>
-    </row>
-    <row r="139" ht="18" customHeight="1">
-      <c r="A139" s="10" t="inlineStr">
+      <c r="I138" s="10" t="inlineStr"/>
+    </row>
+    <row r="139" ht="21" customHeight="1">
+      <c r="A139" s="9" t="inlineStr">
         <is>
           <t>9.6.2</t>
         </is>
       </c>
-      <c r="B139" s="11" t="inlineStr"/>
+      <c r="B139" s="10" t="inlineStr"/>
       <c r="C139" s="11" t="inlineStr"/>
-      <c r="D139" s="12" t="inlineStr">
+      <c r="D139" s="11" t="inlineStr">
         <is>
           <t>비용 통계</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr"/>
-      <c r="F139" s="11" t="inlineStr">
-        <is>
-          <t>비용·수입 집계 통계</t>
-        </is>
-      </c>
-      <c r="G139" s="11" t="inlineStr">
+      <c r="F139" s="12" t="inlineStr">
+        <is>
+          <t>기간별 운송비 수입·원가·이익을 집계하여 수익성 분석. 세부 통계 항목은 추후 확정.</t>
+        </is>
+      </c>
+      <c r="G139" s="10" t="inlineStr">
         <is>
           <t>운영자/관리자</t>
         </is>
       </c>
-      <c r="H139" s="22" t="inlineStr">
+      <c r="H139" s="23" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I139" s="11" t="inlineStr">
-        <is>
-          <t>상세기능 확인 필요</t>
+      <c r="I139" s="10" t="inlineStr">
+        <is>
+          <t>상세기능 추후 확정</t>
         </is>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
-      <c r="A140" s="7" t="inlineStr">
+      <c r="A140" s="6" t="inlineStr">
         <is>
           <t>9.7</t>
         </is>
       </c>
-      <c r="B140" s="8" t="inlineStr"/>
-      <c r="C140" s="9" t="inlineStr">
+      <c r="B140" s="7" t="inlineStr"/>
+      <c r="C140" s="7" t="inlineStr">
         <is>
           <t>데이터 관리</t>
         </is>
       </c>
-      <c r="D140" s="8" t="inlineStr"/>
-      <c r="E140" s="8" t="inlineStr"/>
-      <c r="F140" s="8" t="inlineStr"/>
-      <c r="G140" s="8" t="inlineStr"/>
-      <c r="H140" s="21" t="inlineStr">
+      <c r="D140" s="7" t="inlineStr"/>
+      <c r="E140" s="7" t="inlineStr"/>
+      <c r="F140" s="8" t="inlineStr">
+        <is>
+          <t>시스템 데이터를 안전하게 보관하기 위한 백업 기능.</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="inlineStr"/>
+      <c r="H140" s="22" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I140" s="8" t="inlineStr"/>
-    </row>
-    <row r="141" ht="18" customHeight="1">
-      <c r="A141" s="10" t="inlineStr">
+      <c r="I140" s="7" t="inlineStr"/>
+    </row>
+    <row r="141" ht="26" customHeight="1">
+      <c r="A141" s="9" t="inlineStr">
         <is>
           <t>9.7.1</t>
         </is>
       </c>
-      <c r="B141" s="11" t="inlineStr"/>
+      <c r="B141" s="10" t="inlineStr"/>
       <c r="C141" s="11" t="inlineStr"/>
-      <c r="D141" s="12" t="inlineStr">
+      <c r="D141" s="11" t="inlineStr">
         <is>
           <t>DB 데이터 백업</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr"/>
-      <c r="F141" s="11" t="inlineStr">
-        <is>
-          <t>데이터베이스 자동 백업</t>
-        </is>
-      </c>
-      <c r="G141" s="11" t="inlineStr">
+      <c r="F141" s="12" t="inlineStr">
+        <is>
+          <t>PostgreSQL 데이터베이스 전체 또는 테이블별 자동 백업. 백업 주기: 일별·주별 설정 가능. 백업 파일은 MinIO에 저장.</t>
+        </is>
+      </c>
+      <c r="G141" s="10" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="H141" s="22" t="inlineStr">
+      <c r="H141" s="23" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I141" s="11" t="inlineStr"/>
-    </row>
-    <row r="142" ht="18" customHeight="1">
-      <c r="A142" s="3" t="inlineStr">
+      <c r="I141" s="10" t="inlineStr"/>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B142" s="4" t="inlineStr">
+      <c r="B142" s="3" t="inlineStr">
         <is>
           <t>고객지원</t>
         </is>
       </c>
-      <c r="C142" s="5" t="inlineStr"/>
-      <c r="D142" s="5" t="inlineStr"/>
-      <c r="E142" s="5" t="inlineStr"/>
-      <c r="F142" s="5" t="inlineStr"/>
-      <c r="G142" s="5" t="inlineStr"/>
-      <c r="H142" s="21" t="inlineStr">
+      <c r="C142" s="3" t="inlineStr"/>
+      <c r="D142" s="3" t="inlineStr"/>
+      <c r="E142" s="3" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>회원이 서비스 이용 중 발생하는 문의·공지 정보를 제공하는 기능.</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr"/>
+      <c r="H142" s="22" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I142" s="5" t="inlineStr"/>
-    </row>
-    <row r="143" ht="18" customHeight="1">
-      <c r="A143" s="7" t="inlineStr">
+      <c r="I142" s="3" t="inlineStr"/>
+    </row>
+    <row r="143" ht="24" customHeight="1">
+      <c r="A143" s="6" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
       </c>
-      <c r="B143" s="8" t="inlineStr"/>
-      <c r="C143" s="9" t="inlineStr">
+      <c r="B143" s="7" t="inlineStr"/>
+      <c r="C143" s="7" t="inlineStr">
         <is>
           <t>QnA</t>
         </is>
       </c>
-      <c r="D143" s="8" t="inlineStr"/>
-      <c r="E143" s="8" t="inlineStr"/>
+      <c r="D143" s="7" t="inlineStr"/>
+      <c r="E143" s="7" t="inlineStr"/>
       <c r="F143" s="8" t="inlineStr">
         <is>
-          <t>1:1 문의 등록·조회·답변</t>
-        </is>
-      </c>
-      <c r="G143" s="8" t="inlineStr">
-        <is>
-          <t>회원/운영자/관리자</t>
-        </is>
-      </c>
-      <c r="H143" s="21" t="inlineStr">
+          <t>회원이 1:1 문의를 등록하고 관리자가 답변하는 기능. 문의 등록 후 처리상태(접수·처리중·완료) 확인 가능.</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t>회원/관리자</t>
+        </is>
+      </c>
+      <c r="H143" s="22" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I143" s="8" t="inlineStr"/>
-    </row>
-    <row r="144" ht="18" customHeight="1">
-      <c r="A144" s="7" t="inlineStr">
+      <c r="I143" s="7" t="inlineStr"/>
+    </row>
+    <row r="144" ht="23" customHeight="1">
+      <c r="A144" s="6" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="B144" s="8" t="inlineStr"/>
-      <c r="C144" s="9" t="inlineStr">
+      <c r="B144" s="7" t="inlineStr"/>
+      <c r="C144" s="7" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="D144" s="8" t="inlineStr"/>
-      <c r="E144" s="8" t="inlineStr"/>
+      <c r="D144" s="7" t="inlineStr"/>
+      <c r="E144" s="7" t="inlineStr"/>
       <c r="F144" s="8" t="inlineStr">
         <is>
-          <t>자주 묻는 질문 관리 및 조회</t>
-        </is>
-      </c>
-      <c r="G144" s="8" t="inlineStr">
+          <t>자주 묻는 질문과 답변을 카테고리별로 관리. 관리자가 FAQ를 등록·수정·삭제하며 회원은 조회만 가능.</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
         <is>
           <t>회원/관리자</t>
         </is>
       </c>
-      <c r="H144" s="21" t="inlineStr">
+      <c r="H144" s="22" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I144" s="8" t="inlineStr"/>
-    </row>
-    <row r="145" ht="18" customHeight="1">
-      <c r="A145" s="7" t="inlineStr">
+      <c r="I144" s="7" t="inlineStr"/>
+    </row>
+    <row r="145" ht="24" customHeight="1">
+      <c r="A145" s="6" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="B145" s="8" t="inlineStr"/>
-      <c r="C145" s="9" t="inlineStr">
+      <c r="B145" s="7" t="inlineStr"/>
+      <c r="C145" s="7" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="D145" s="8" t="inlineStr"/>
-      <c r="E145" s="8" t="inlineStr"/>
+      <c r="D145" s="7" t="inlineStr"/>
+      <c r="E145" s="7" t="inlineStr"/>
       <c r="F145" s="8" t="inlineStr">
         <is>
-          <t>서비스 공지 등록·수정·삭제·조회</t>
-        </is>
-      </c>
-      <c r="G145" s="8" t="inlineStr">
+          <t>서비스 변경사항·이벤트 등 공지를 등록·관리. 관리자가 등록하고 전체 회원에게 공개. 중요 공지는 상단 고정 가능.</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr">
         <is>
           <t>회원/관리자</t>
         </is>
       </c>
-      <c r="H145" s="21" t="inlineStr">
+      <c r="H145" s="22" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
       </c>
-      <c r="I145" s="8" t="inlineStr"/>
+      <c r="I145" s="7" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="23" t="inlineStr">
+      <c r="A146" s="24" t="inlineStr">
         <is>
           <t>【범례】</t>
         </is>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
-      <c r="A147" s="3" t="inlineStr">
-        <is>
-          <t>대분류</t>
-        </is>
-      </c>
-      <c r="B147" s="7" t="inlineStr">
-        <is>
-          <t>중분류</t>
-        </is>
-      </c>
-      <c r="C147" s="24" t="inlineStr">
-        <is>
-          <t>소분류</t>
-        </is>
-      </c>
-      <c r="D147" s="25" t="inlineStr">
-        <is>
-          <t>세부기능</t>
-        </is>
-      </c>
-      <c r="E147" s="26" t="inlineStr">
+      <c r="A147" s="25" t="inlineStr">
+        <is>
+          <t>대분류(L1)</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>중분류(L2)</t>
+        </is>
+      </c>
+      <c r="C147" s="26" t="inlineStr">
+        <is>
+          <t>소분류(L3)</t>
+        </is>
+      </c>
+      <c r="D147" s="27" t="inlineStr">
+        <is>
+          <t>세부기능(L4)</t>
+        </is>
+      </c>
+      <c r="E147" s="28" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="F147" s="27" t="inlineStr">
+      <c r="F147" s="29" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="G147" s="28" t="inlineStr">
+      <c r="G147" s="30" t="inlineStr">
         <is>
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="H147" s="29" t="inlineStr">
+      <c r="H147" s="31" t="inlineStr">
         <is>
           <t>Phase 4</t>
         </is>
